--- a/database/event/7441/event_7441_evp_summary.xlsx
+++ b/database/event/7441/event_7441_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.8239</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.3248</v>
       </c>
       <c r="D2" t="n">
         <v>3.5473</v>
@@ -545,7 +545,7 @@
         <v>9.130699999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.808</v>
       </c>
       <c r="D3" t="n">
         <v>3.2672</v>
@@ -591,7 +591,7 @@
         <v>7.5436</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.6246</v>
       </c>
       <c r="D4" t="n">
         <v>2.6261</v>
@@ -637,7 +637,7 @@
         <v>6.8166</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.0825</v>
       </c>
       <c r="D5" t="n">
         <v>2.3324</v>
@@ -683,7 +683,7 @@
         <v>6.2317</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.6464</v>
       </c>
       <c r="D6" t="n">
         <v>2.0961</v>
@@ -729,7 +729,7 @@
         <v>6.2206</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4.6382</v>
       </c>
       <c r="D7" t="n">
         <v>2.0916</v>
@@ -775,7 +775,7 @@
         <v>6.0544</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4.5142</v>
       </c>
       <c r="D8" t="n">
         <v>2.0245</v>
@@ -821,7 +821,7 @@
         <v>5.8425</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4.3562</v>
       </c>
       <c r="D9" t="n">
         <v>1.9389</v>
@@ -867,7 +867,7 @@
         <v>5.6364</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4.2026</v>
       </c>
       <c r="D10" t="n">
         <v>1.8556</v>
@@ -913,7 +913,7 @@
         <v>5.5982</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4.1741</v>
       </c>
       <c r="D11" t="n">
         <v>1.8402</v>
@@ -959,7 +959,7 @@
         <v>5.5753</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>4.157</v>
       </c>
       <c r="D12" t="n">
         <v>1.8309</v>
@@ -1005,7 +1005,7 @@
         <v>5.5236</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4.1185</v>
       </c>
       <c r="D13" t="n">
         <v>1.81</v>
@@ -1051,7 +1051,7 @@
         <v>5.4394</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4.0557</v>
       </c>
       <c r="D14" t="n">
         <v>1.776</v>
@@ -1097,7 +1097,7 @@
         <v>5.333</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3.9764</v>
       </c>
       <c r="D15" t="n">
         <v>1.7331</v>
@@ -1143,7 +1143,7 @@
         <v>5.3273</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.9721</v>
       </c>
       <c r="D16" t="n">
         <v>1.7307</v>
@@ -1189,7 +1189,7 @@
         <v>5.2084</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3.8835</v>
       </c>
       <c r="D17" t="n">
         <v>1.6827</v>
@@ -1235,7 +1235,7 @@
         <v>4.9993</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3.7275</v>
       </c>
       <c r="D18" t="n">
         <v>1.5982</v>
@@ -1281,7 +1281,7 @@
         <v>4.6683</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.4807</v>
       </c>
       <c r="D19" t="n">
         <v>1.4645</v>
@@ -1327,7 +1327,7 @@
         <v>4.6475</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.4652</v>
       </c>
       <c r="D20" t="n">
         <v>1.4561</v>
@@ -1373,7 +1373,7 @@
         <v>4.5716</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3.4086</v>
       </c>
       <c r="D21" t="n">
         <v>1.4255</v>
@@ -1419,7 +1419,7 @@
         <v>4.5377</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3.3834</v>
       </c>
       <c r="D22" t="n">
         <v>1.4118</v>
@@ -1465,7 +1465,7 @@
         <v>4.3019</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3.2076</v>
       </c>
       <c r="D23" t="n">
         <v>1.3165</v>
@@ -1511,7 +1511,7 @@
         <v>4.175</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3.1129</v>
       </c>
       <c r="D24" t="n">
         <v>1.2652</v>
@@ -1557,7 +1557,7 @@
         <v>4.1062</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3.0616</v>
       </c>
       <c r="D25" t="n">
         <v>1.2375</v>
@@ -1603,7 +1603,7 @@
         <v>4.0856</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>3.0463</v>
       </c>
       <c r="D26" t="n">
         <v>1.2291</v>
@@ -1649,7 +1649,7 @@
         <v>4.0715</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3.0358</v>
       </c>
       <c r="D27" t="n">
         <v>1.2234</v>
@@ -1695,7 +1695,7 @@
         <v>4.0596</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3.0269</v>
       </c>
       <c r="D28" t="n">
         <v>1.2186</v>
@@ -1741,7 +1741,7 @@
         <v>4.0131</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2.9922</v>
       </c>
       <c r="D29" t="n">
         <v>1.1998</v>
@@ -1787,7 +1787,7 @@
         <v>3.9436</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2.9404</v>
       </c>
       <c r="D30" t="n">
         <v>1.1718</v>
@@ -1833,7 +1833,7 @@
         <v>3.8956</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.9046</v>
       </c>
       <c r="D31" t="n">
         <v>1.1524</v>
@@ -1879,7 +1879,7 @@
         <v>3.8593</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2.8775</v>
       </c>
       <c r="D32" t="n">
         <v>1.1377</v>
@@ -1925,7 +1925,7 @@
         <v>3.8563</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2.8753</v>
       </c>
       <c r="D33" t="n">
         <v>1.1365</v>
@@ -1971,7 +1971,7 @@
         <v>3.8229</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.8504</v>
       </c>
       <c r="D34" t="n">
         <v>1.123</v>
@@ -2017,7 +2017,7 @@
         <v>3.8192</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2.8476</v>
       </c>
       <c r="D35" t="n">
         <v>1.1215</v>
@@ -2063,7 +2063,7 @@
         <v>3.8171</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.8461</v>
       </c>
       <c r="D36" t="n">
         <v>1.1207</v>
@@ -2109,7 +2109,7 @@
         <v>3.7031</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2.7611</v>
       </c>
       <c r="D37" t="n">
         <v>1.0746</v>
@@ -2155,7 +2155,7 @@
         <v>3.5805</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.6697</v>
       </c>
       <c r="D38" t="n">
         <v>1.0251</v>
@@ -2201,7 +2201,7 @@
         <v>3.3778</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2.5185</v>
       </c>
       <c r="D39" t="n">
         <v>0.9432</v>
@@ -2247,7 +2247,7 @@
         <v>3.3537</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.5006</v>
       </c>
       <c r="D40" t="n">
         <v>0.9335</v>
@@ -2293,7 +2293,7 @@
         <v>3.3169</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2.4731</v>
       </c>
       <c r="D41" t="n">
         <v>0.9186</v>
@@ -2339,7 +2339,7 @@
         <v>3.3011</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2.4613</v>
       </c>
       <c r="D42" t="n">
         <v>0.9122</v>
@@ -2385,7 +2385,7 @@
         <v>3.2891</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2.4524</v>
       </c>
       <c r="D43" t="n">
         <v>0.9074</v>
@@ -2431,7 +2431,7 @@
         <v>3.2783</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2.4443</v>
       </c>
       <c r="D44" t="n">
         <v>0.903</v>
@@ -2477,7 +2477,7 @@
         <v>3.2521</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2.4248</v>
       </c>
       <c r="D45" t="n">
         <v>0.8924</v>
@@ -2523,7 +2523,7 @@
         <v>3.1314</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2.3348</v>
       </c>
       <c r="D46" t="n">
         <v>0.8437</v>
@@ -2569,7 +2569,7 @@
         <v>2.976</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2.2189</v>
       </c>
       <c r="D47" t="n">
         <v>0.7809</v>
@@ -2615,7 +2615,7 @@
         <v>2.905</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2.166</v>
       </c>
       <c r="D48" t="n">
         <v>0.7522</v>
@@ -2661,7 +2661,7 @@
         <v>2.9002</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>2.1624</v>
       </c>
       <c r="D49" t="n">
         <v>0.7503</v>
@@ -2707,7 +2707,7 @@
         <v>2.8149</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2.0988</v>
       </c>
       <c r="D50" t="n">
         <v>0.7158</v>
@@ -2753,7 +2753,7 @@
         <v>2.794</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2.0832</v>
       </c>
       <c r="D51" t="n">
         <v>0.7074</v>
@@ -2799,7 +2799,7 @@
         <v>2.7801</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2.0729</v>
       </c>
       <c r="D52" t="n">
         <v>0.7017</v>
@@ -2845,7 +2845,7 @@
         <v>2.7699</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2.0653</v>
       </c>
       <c r="D53" t="n">
         <v>0.6976</v>
@@ -2891,7 +2891,7 @@
         <v>2.6953</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2.0097</v>
       </c>
       <c r="D54" t="n">
         <v>0.6675</v>
@@ -2937,7 +2937,7 @@
         <v>2.5539</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1.9042</v>
       </c>
       <c r="D55" t="n">
         <v>0.6104000000000001</v>
@@ -2983,7 +2983,7 @@
         <v>2.4426</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1.8212</v>
       </c>
       <c r="D56" t="n">
         <v>0.5654</v>
@@ -3029,7 +3029,7 @@
         <v>2.3858</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1.7789</v>
       </c>
       <c r="D57" t="n">
         <v>0.5424</v>
@@ -3075,7 +3075,7 @@
         <v>2.2727</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1.6946</v>
       </c>
       <c r="D58" t="n">
         <v>0.4968</v>
@@ -3121,7 +3121,7 @@
         <v>2.1976</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1.6386</v>
       </c>
       <c r="D59" t="n">
         <v>0.4664</v>
@@ -3167,7 +3167,7 @@
         <v>2.1177</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1.579</v>
       </c>
       <c r="D60" t="n">
         <v>0.4341</v>
@@ -3213,7 +3213,7 @@
         <v>2.0392</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1.5205</v>
       </c>
       <c r="D61" t="n">
         <v>0.4024</v>
@@ -3259,7 +3259,7 @@
         <v>2.0346</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1.517</v>
       </c>
       <c r="D62" t="n">
         <v>0.4006</v>
@@ -3305,7 +3305,7 @@
         <v>1.937</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1.4443</v>
       </c>
       <c r="D63" t="n">
         <v>0.3611</v>
@@ -3351,7 +3351,7 @@
         <v>1.9276</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1.4372</v>
       </c>
       <c r="D64" t="n">
         <v>0.3573</v>
@@ -3397,7 +3397,7 @@
         <v>1.8671</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1.3921</v>
       </c>
       <c r="D65" t="n">
         <v>0.3329</v>
@@ -3443,7 +3443,7 @@
         <v>1.8599</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1.3868</v>
       </c>
       <c r="D66" t="n">
         <v>0.33</v>
@@ -3489,7 +3489,7 @@
         <v>1.854</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1.3824</v>
       </c>
       <c r="D67" t="n">
         <v>0.3276</v>
@@ -3535,7 +3535,7 @@
         <v>1.799</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1.3414</v>
       </c>
       <c r="D68" t="n">
         <v>0.3054</v>
@@ -3581,7 +3581,7 @@
         <v>1.7605</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1.3127</v>
       </c>
       <c r="D69" t="n">
         <v>0.2898</v>
@@ -3627,7 +3627,7 @@
         <v>1.6997</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1.2673</v>
       </c>
       <c r="D70" t="n">
         <v>0.2653</v>
@@ -3673,7 +3673,7 @@
         <v>1.6728</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1.2473</v>
       </c>
       <c r="D71" t="n">
         <v>0.2544</v>
@@ -3719,7 +3719,7 @@
         <v>1.6506</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1.2307</v>
       </c>
       <c r="D72" t="n">
         <v>0.2454</v>
@@ -3765,7 +3765,7 @@
         <v>1.6263</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1.2126</v>
       </c>
       <c r="D73" t="n">
         <v>0.2356</v>
@@ -3811,7 +3811,7 @@
         <v>1.5023</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1.1201</v>
       </c>
       <c r="D74" t="n">
         <v>0.1855</v>
@@ -3857,7 +3857,7 @@
         <v>1.4448</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1.0773</v>
       </c>
       <c r="D75" t="n">
         <v>0.1623</v>
@@ -3903,7 +3903,7 @@
         <v>1.4078</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>1.0497</v>
       </c>
       <c r="D76" t="n">
         <v>0.1474</v>
@@ -3949,7 +3949,7 @@
         <v>1.3516</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>1.0078</v>
       </c>
       <c r="D77" t="n">
         <v>0.1247</v>
@@ -3995,7 +3995,7 @@
         <v>1.3023</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="D78" t="n">
         <v>0.1047</v>
@@ -4041,7 +4041,7 @@
         <v>1.2844</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>0.9577</v>
       </c>
       <c r="D79" t="n">
         <v>0.0975</v>
@@ -4087,7 +4087,7 @@
         <v>1.2645</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>0.9428</v>
       </c>
       <c r="D80" t="n">
         <v>0.0895</v>
@@ -4133,7 +4133,7 @@
         <v>1.2561</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.9366</v>
       </c>
       <c r="D81" t="n">
         <v>0.0861</v>
@@ -4179,7 +4179,7 @@
         <v>1.1906</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.8877</v>
       </c>
       <c r="D82" t="n">
         <v>0.0596</v>
@@ -4225,7 +4225,7 @@
         <v>1.0747</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.8013</v>
       </c>
       <c r="D83" t="n">
         <v>0.0128</v>
@@ -4271,7 +4271,7 @@
         <v>1.0604</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.7906</v>
       </c>
       <c r="D84" t="n">
         <v>0.007</v>
@@ -4317,7 +4317,7 @@
         <v>0.9921</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.7397</v>
       </c>
       <c r="D85" t="n">
         <v>-0.0206</v>
@@ -4363,7 +4363,7 @@
         <v>0.9305</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.6938</v>
       </c>
       <c r="D86" t="n">
         <v>-0.0455</v>
@@ -4409,7 +4409,7 @@
         <v>0.837</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>0.6241</v>
       </c>
       <c r="D87" t="n">
         <v>-0.0832</v>
@@ -4455,7 +4455,7 @@
         <v>0.7724</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>0.5759</v>
       </c>
       <c r="D88" t="n">
         <v>-0.1093</v>
@@ -4501,7 +4501,7 @@
         <v>0.7718</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.5755</v>
       </c>
       <c r="D89" t="n">
         <v>-0.1096</v>
@@ -4547,7 +4547,7 @@
         <v>0.705</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D90" t="n">
         <v>-0.1366</v>
@@ -4593,7 +4593,7 @@
         <v>0.6075</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>0.453</v>
       </c>
       <c r="D91" t="n">
         <v>-0.1759</v>
@@ -4639,7 +4639,7 @@
         <v>0.6035</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="D92" t="n">
         <v>-0.1776</v>
@@ -4685,7 +4685,7 @@
         <v>0.5904</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.4402</v>
       </c>
       <c r="D93" t="n">
         <v>-0.1829</v>
@@ -4731,7 +4731,7 @@
         <v>0.5102</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.3804</v>
       </c>
       <c r="D94" t="n">
         <v>-0.2153</v>
@@ -4777,7 +4777,7 @@
         <v>0.4593</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.3425</v>
       </c>
       <c r="D95" t="n">
         <v>-0.2358</v>
@@ -4823,7 +4823,7 @@
         <v>0.3789</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.2825</v>
       </c>
       <c r="D96" t="n">
         <v>-0.2683</v>
@@ -4869,7 +4869,7 @@
         <v>0.3446</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>0.2569</v>
       </c>
       <c r="D97" t="n">
         <v>-0.2822</v>
@@ -4915,7 +4915,7 @@
         <v>0.2536</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="D98" t="n">
         <v>-0.3189</v>
@@ -4961,7 +4961,7 @@
         <v>0.2464</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.1837</v>
       </c>
       <c r="D99" t="n">
         <v>-0.3218</v>
@@ -5007,7 +5007,7 @@
         <v>0.1905</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="D100" t="n">
         <v>-0.3444</v>
@@ -5053,7 +5053,7 @@
         <v>0.1389</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.1036</v>
       </c>
       <c r="D101" t="n">
         <v>-0.3652</v>
@@ -5099,7 +5099,7 @@
         <v>-0.0336</v>
       </c>
       <c r="C102" t="n">
-        <v>-0</v>
+        <v>-0.0251</v>
       </c>
       <c r="D102" t="n">
         <v>-0.4349</v>
@@ -5145,7 +5145,7 @@
         <v>-0.0738</v>
       </c>
       <c r="C103" t="n">
-        <v>-0</v>
+        <v>-0.055</v>
       </c>
       <c r="D103" t="n">
         <v>-0.4512</v>
@@ -5191,7 +5191,7 @@
         <v>-0.1054</v>
       </c>
       <c r="C104" t="n">
-        <v>-0</v>
+        <v>-0.0786</v>
       </c>
       <c r="D104" t="n">
         <v>-0.4639</v>
@@ -5237,7 +5237,7 @@
         <v>-0.1097</v>
       </c>
       <c r="C105" t="n">
-        <v>-0</v>
+        <v>-0.0818</v>
       </c>
       <c r="D105" t="n">
         <v>-0.4657</v>
@@ -5283,7 +5283,7 @@
         <v>-0.2227</v>
       </c>
       <c r="C106" t="n">
-        <v>-0</v>
+        <v>-0.166</v>
       </c>
       <c r="D106" t="n">
         <v>-0.5113</v>
@@ -5329,7 +5329,7 @@
         <v>-0.2989</v>
       </c>
       <c r="C107" t="n">
-        <v>-0</v>
+        <v>-0.2229</v>
       </c>
       <c r="D107" t="n">
         <v>-0.5421</v>
@@ -5375,7 +5375,7 @@
         <v>-0.3226</v>
       </c>
       <c r="C108" t="n">
-        <v>-0</v>
+        <v>-0.2405</v>
       </c>
       <c r="D108" t="n">
         <v>-0.5517</v>
@@ -5421,7 +5421,7 @@
         <v>-0.357</v>
       </c>
       <c r="C109" t="n">
-        <v>-0</v>
+        <v>-0.2662</v>
       </c>
       <c r="D109" t="n">
         <v>-0.5656</v>
@@ -5467,7 +5467,7 @@
         <v>-0.3689</v>
       </c>
       <c r="C110" t="n">
-        <v>-0</v>
+        <v>-0.2751</v>
       </c>
       <c r="D110" t="n">
         <v>-0.5704</v>
@@ -5513,7 +5513,7 @@
         <v>-0.3911</v>
       </c>
       <c r="C111" t="n">
-        <v>-0</v>
+        <v>-0.2916</v>
       </c>
       <c r="D111" t="n">
         <v>-0.5794</v>
@@ -5559,7 +5559,7 @@
         <v>-0.4027</v>
       </c>
       <c r="C112" t="n">
-        <v>-0</v>
+        <v>-0.3003</v>
       </c>
       <c r="D112" t="n">
         <v>-0.584</v>
@@ -5605,7 +5605,7 @@
         <v>-0.4807</v>
       </c>
       <c r="C113" t="n">
-        <v>-0</v>
+        <v>-0.3584</v>
       </c>
       <c r="D113" t="n">
         <v>-0.6156</v>
@@ -5651,7 +5651,7 @@
         <v>-0.5164</v>
       </c>
       <c r="C114" t="n">
-        <v>-0</v>
+        <v>-0.385</v>
       </c>
       <c r="D114" t="n">
         <v>-0.63</v>
@@ -5697,7 +5697,7 @@
         <v>-0.6225000000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>-0</v>
+        <v>-0.4641</v>
       </c>
       <c r="D115" t="n">
         <v>-0.6728</v>
@@ -5743,7 +5743,7 @@
         <v>-0.6291</v>
       </c>
       <c r="C116" t="n">
-        <v>-0</v>
+        <v>-0.4691</v>
       </c>
       <c r="D116" t="n">
         <v>-0.6755</v>
@@ -5789,7 +5789,7 @@
         <v>-0.6786</v>
       </c>
       <c r="C117" t="n">
-        <v>-0</v>
+        <v>-0.506</v>
       </c>
       <c r="D117" t="n">
         <v>-0.6955</v>
@@ -5835,7 +5835,7 @@
         <v>-0.7005</v>
       </c>
       <c r="C118" t="n">
-        <v>-0</v>
+        <v>-0.5223</v>
       </c>
       <c r="D118" t="n">
         <v>-0.7043</v>
@@ -5881,7 +5881,7 @@
         <v>-0.736</v>
       </c>
       <c r="C119" t="n">
-        <v>-0</v>
+        <v>-0.5488</v>
       </c>
       <c r="D119" t="n">
         <v>-0.7187</v>
@@ -5927,7 +5927,7 @@
         <v>-0.7465000000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>-0</v>
+        <v>-0.5566</v>
       </c>
       <c r="D120" t="n">
         <v>-0.7229</v>
@@ -5973,7 +5973,7 @@
         <v>-0.7541</v>
       </c>
       <c r="C121" t="n">
-        <v>-0</v>
+        <v>-0.5623</v>
       </c>
       <c r="D121" t="n">
         <v>-0.726</v>
@@ -6019,7 +6019,7 @@
         <v>-0.8224</v>
       </c>
       <c r="C122" t="n">
-        <v>-0</v>
+        <v>-0.6132</v>
       </c>
       <c r="D122" t="n">
         <v>-0.7536</v>
@@ -6065,7 +6065,7 @@
         <v>-0.8767</v>
       </c>
       <c r="C123" t="n">
-        <v>-0</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="D123" t="n">
         <v>-0.7755</v>
@@ -6111,7 +6111,7 @@
         <v>-1.0162</v>
       </c>
       <c r="C124" t="n">
-        <v>-0</v>
+        <v>-0.7577</v>
       </c>
       <c r="D124" t="n">
         <v>-0.8319</v>
@@ -6157,7 +6157,7 @@
         <v>-1.1878</v>
       </c>
       <c r="C125" t="n">
-        <v>-0</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="D125" t="n">
         <v>-0.9012</v>
@@ -6203,7 +6203,7 @@
         <v>-1.2568</v>
       </c>
       <c r="C126" t="n">
-        <v>-0</v>
+        <v>-0.9371</v>
       </c>
       <c r="D126" t="n">
         <v>-0.9291</v>
@@ -6249,7 +6249,7 @@
         <v>-1.2955</v>
       </c>
       <c r="C127" t="n">
-        <v>-0</v>
+        <v>-0.9659</v>
       </c>
       <c r="D127" t="n">
         <v>-0.9447</v>
@@ -6295,7 +6295,7 @@
         <v>-1.2967</v>
       </c>
       <c r="C128" t="n">
-        <v>-0</v>
+        <v>-0.9668</v>
       </c>
       <c r="D128" t="n">
         <v>-0.9452</v>
@@ -6341,7 +6341,7 @@
         <v>-1.3269</v>
       </c>
       <c r="C129" t="n">
-        <v>-0</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="D129" t="n">
         <v>-0.9574</v>
@@ -6387,7 +6387,7 @@
         <v>-1.417</v>
       </c>
       <c r="C130" t="n">
-        <v>-0</v>
+        <v>-1.0565</v>
       </c>
       <c r="D130" t="n">
         <v>-0.9938</v>
@@ -6433,7 +6433,7 @@
         <v>-1.5971</v>
       </c>
       <c r="C131" t="n">
-        <v>-0</v>
+        <v>-1.1908</v>
       </c>
       <c r="D131" t="n">
         <v>-1.0666</v>
@@ -6479,7 +6479,7 @@
         <v>-1.6329</v>
       </c>
       <c r="C132" t="n">
-        <v>-0</v>
+        <v>-1.2175</v>
       </c>
       <c r="D132" t="n">
         <v>-1.081</v>
@@ -6525,7 +6525,7 @@
         <v>-1.6546</v>
       </c>
       <c r="C133" t="n">
-        <v>-0</v>
+        <v>-1.2337</v>
       </c>
       <c r="D133" t="n">
         <v>-1.0898</v>
@@ -6571,7 +6571,7 @@
         <v>-1.6638</v>
       </c>
       <c r="C134" t="n">
-        <v>-0</v>
+        <v>-1.2406</v>
       </c>
       <c r="D134" t="n">
         <v>-1.0935</v>
@@ -6617,7 +6617,7 @@
         <v>-1.7094</v>
       </c>
       <c r="C135" t="n">
-        <v>-0</v>
+        <v>-1.2746</v>
       </c>
       <c r="D135" t="n">
         <v>-1.1119</v>
@@ -6663,7 +6663,7 @@
         <v>-1.715</v>
       </c>
       <c r="C136" t="n">
-        <v>-0</v>
+        <v>-1.2787</v>
       </c>
       <c r="D136" t="n">
         <v>-1.1142</v>
@@ -6709,7 +6709,7 @@
         <v>-1.8294</v>
       </c>
       <c r="C137" t="n">
-        <v>-0</v>
+        <v>-1.364</v>
       </c>
       <c r="D137" t="n">
         <v>-1.1604</v>
@@ -6755,7 +6755,7 @@
         <v>-1.9106</v>
       </c>
       <c r="C138" t="n">
-        <v>-0</v>
+        <v>-1.4246</v>
       </c>
       <c r="D138" t="n">
         <v>-1.1932</v>
@@ -6801,7 +6801,7 @@
         <v>-1.9538</v>
       </c>
       <c r="C139" t="n">
-        <v>-0</v>
+        <v>-1.4568</v>
       </c>
       <c r="D139" t="n">
         <v>-1.2107</v>
@@ -6847,7 +6847,7 @@
         <v>-2.0901</v>
       </c>
       <c r="C140" t="n">
-        <v>-0</v>
+        <v>-1.5584</v>
       </c>
       <c r="D140" t="n">
         <v>-1.2657</v>
@@ -6893,7 +6893,7 @@
         <v>-2.2061</v>
       </c>
       <c r="C141" t="n">
-        <v>-0</v>
+        <v>-1.6449</v>
       </c>
       <c r="D141" t="n">
         <v>-1.3126</v>
@@ -6939,7 +6939,7 @@
         <v>-2.2208</v>
       </c>
       <c r="C142" t="n">
-        <v>-0</v>
+        <v>-1.6559</v>
       </c>
       <c r="D142" t="n">
         <v>-1.3185</v>
@@ -6985,7 +6985,7 @@
         <v>-2.2294</v>
       </c>
       <c r="C143" t="n">
-        <v>-0</v>
+        <v>-1.6623</v>
       </c>
       <c r="D143" t="n">
         <v>-1.322</v>
@@ -7031,7 +7031,7 @@
         <v>-2.4083</v>
       </c>
       <c r="C144" t="n">
-        <v>-0</v>
+        <v>-1.7957</v>
       </c>
       <c r="D144" t="n">
         <v>-1.3943</v>
@@ -7077,7 +7077,7 @@
         <v>-2.4571</v>
       </c>
       <c r="C145" t="n">
-        <v>-0</v>
+        <v>-1.832</v>
       </c>
       <c r="D145" t="n">
         <v>-1.414</v>
@@ -7123,7 +7123,7 @@
         <v>-2.4726</v>
       </c>
       <c r="C146" t="n">
-        <v>-0</v>
+        <v>-1.8436</v>
       </c>
       <c r="D146" t="n">
         <v>-1.4202</v>
@@ -7169,7 +7169,7 @@
         <v>-2.496</v>
       </c>
       <c r="C147" t="n">
-        <v>-0</v>
+        <v>-1.8611</v>
       </c>
       <c r="D147" t="n">
         <v>-1.4297</v>
@@ -7215,7 +7215,7 @@
         <v>-2.6837</v>
       </c>
       <c r="C148" t="n">
-        <v>-0</v>
+        <v>-2.001</v>
       </c>
       <c r="D148" t="n">
         <v>-1.5055</v>
@@ -7261,7 +7261,7 @@
         <v>-2.6913</v>
       </c>
       <c r="C149" t="n">
-        <v>-0</v>
+        <v>-2.0067</v>
       </c>
       <c r="D149" t="n">
         <v>-1.5086</v>
@@ -7307,7 +7307,7 @@
         <v>-2.6934</v>
       </c>
       <c r="C150" t="n">
-        <v>-0</v>
+        <v>-2.0082</v>
       </c>
       <c r="D150" t="n">
         <v>-1.5094</v>
@@ -7353,7 +7353,7 @@
         <v>-2.7388</v>
       </c>
       <c r="C151" t="n">
-        <v>-0</v>
+        <v>-2.0421</v>
       </c>
       <c r="D151" t="n">
         <v>-1.5278</v>
@@ -7399,7 +7399,7 @@
         <v>-2.8387</v>
       </c>
       <c r="C152" t="n">
-        <v>-0</v>
+        <v>-2.1166</v>
       </c>
       <c r="D152" t="n">
         <v>-1.5681</v>
@@ -7445,7 +7445,7 @@
         <v>-3</v>
       </c>
       <c r="C153" t="n">
-        <v>-0</v>
+        <v>-2.2368</v>
       </c>
       <c r="D153" t="n">
         <v>-1.6333</v>
@@ -7491,7 +7491,7 @@
         <v>-3.0767</v>
       </c>
       <c r="C154" t="n">
-        <v>-0</v>
+        <v>-2.294</v>
       </c>
       <c r="D154" t="n">
         <v>-1.6643</v>
@@ -7537,7 +7537,7 @@
         <v>-3.0989</v>
       </c>
       <c r="C155" t="n">
-        <v>-0</v>
+        <v>-2.3106</v>
       </c>
       <c r="D155" t="n">
         <v>-1.6732</v>
@@ -7583,7 +7583,7 @@
         <v>-3.1997</v>
       </c>
       <c r="C156" t="n">
-        <v>-0</v>
+        <v>-2.3857</v>
       </c>
       <c r="D156" t="n">
         <v>-1.714</v>
@@ -7629,7 +7629,7 @@
         <v>-3.674</v>
       </c>
       <c r="C157" t="n">
-        <v>-0</v>
+        <v>-2.7394</v>
       </c>
       <c r="D157" t="n">
         <v>-1.9056</v>
@@ -7675,7 +7675,7 @@
         <v>-3.7049</v>
       </c>
       <c r="C158" t="n">
-        <v>-0</v>
+        <v>-2.7624</v>
       </c>
       <c r="D158" t="n">
         <v>-1.9181</v>
@@ -7721,7 +7721,7 @@
         <v>-3.7242</v>
       </c>
       <c r="C159" t="n">
-        <v>-0</v>
+        <v>-2.7768</v>
       </c>
       <c r="D159" t="n">
         <v>-1.9259</v>
@@ -7767,7 +7767,7 @@
         <v>-5.0678</v>
       </c>
       <c r="C160" t="n">
-        <v>-0</v>
+        <v>-3.7786</v>
       </c>
       <c r="D160" t="n">
         <v>-2.4686</v>
@@ -7813,7 +7813,7 @@
         <v>-6.4826</v>
       </c>
       <c r="C161" t="n">
-        <v>-0</v>
+        <v>-4.8335</v>
       </c>
       <c r="D161" t="n">
         <v>-3.0402</v>

--- a/database/event/7441/event_7441_evp_summary.xlsx
+++ b/database/event/7441/event_7441_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.3248</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5473</v>
+        <v>3.4699</v>
       </c>
       <c r="E2" t="n">
         <v>9.8239</v>
@@ -548,7 +548,7 @@
         <v>6.808</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2672</v>
+        <v>3.1938</v>
       </c>
       <c r="E3" t="n">
         <v>9.130699999999999</v>
@@ -594,7 +594,7 @@
         <v>5.6246</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6261</v>
+        <v>2.5615</v>
       </c>
       <c r="E4" t="n">
         <v>7.5436</v>
@@ -640,7 +640,7 @@
         <v>5.0825</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3324</v>
+        <v>2.2718</v>
       </c>
       <c r="E5" t="n">
         <v>6.8166</v>
@@ -686,7 +686,7 @@
         <v>4.6464</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0961</v>
+        <v>2.0388</v>
       </c>
       <c r="E6" t="n">
         <v>6.2317</v>
@@ -698,7 +698,7 @@
         <v>-0.2318</v>
       </c>
       <c r="H6" t="n">
-        <v>8.6655</v>
+        <v>8.505100000000001</v>
       </c>
       <c r="I6" t="n">
         <v>8.8691</v>
@@ -732,7 +732,7 @@
         <v>4.6382</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0916</v>
+        <v>2.0344</v>
       </c>
       <c r="E7" t="n">
         <v>6.2206</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.0544</v>
+        <v>5.9695</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5142</v>
+        <v>4.4509</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0245</v>
+        <v>1.9343</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0544</v>
+        <v>5.9695</v>
       </c>
       <c r="F8" t="n">
-        <v>6.0544</v>
+        <v>5.9695</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1902</v>
+        <v>7.0571</v>
       </c>
       <c r="I8" t="n">
         <v>7.3591</v>
@@ -824,7 +824,7 @@
         <v>4.3562</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9389</v>
+        <v>1.8837</v>
       </c>
       <c r="E9" t="n">
         <v>5.8425</v>
@@ -870,7 +870,7 @@
         <v>4.2026</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8556</v>
+        <v>1.8016</v>
       </c>
       <c r="E10" t="n">
         <v>5.6364</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.5982</v>
+        <v>5.56</v>
       </c>
       <c r="C11" t="n">
-        <v>4.1741</v>
+        <v>4.1456</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8402</v>
+        <v>1.7712</v>
       </c>
       <c r="E11" t="n">
-        <v>5.5982</v>
+        <v>5.56</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2214</v>
+        <v>5.56</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3768</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8841</v>
+        <v>6.415</v>
       </c>
       <c r="I11" t="n">
-        <v>6.0223</v>
+        <v>6.469</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3768</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>324</v>
+        <v>256</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>6.399100000000001</v>
+        <v>6.469</v>
       </c>
       <c r="N11" t="n">
-        <v>364</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.5753</v>
+        <v>5.5287</v>
       </c>
       <c r="C12" t="n">
-        <v>4.157</v>
+        <v>4.1223</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8309</v>
+        <v>1.7587</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5753</v>
+        <v>5.5287</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5753</v>
+        <v>5.1519</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.3768</v>
       </c>
       <c r="H12" t="n">
-        <v>6.439</v>
+        <v>5.7752</v>
       </c>
       <c r="I12" t="n">
-        <v>6.469</v>
+        <v>6.0223</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.3768</v>
       </c>
       <c r="K12" t="n">
-        <v>256</v>
+        <v>324</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>6.469</v>
+        <v>6.399100000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13">
@@ -1008,7 +1008,7 @@
         <v>4.1185</v>
       </c>
       <c r="D13" t="n">
-        <v>1.81</v>
+        <v>1.7567</v>
       </c>
       <c r="E13" t="n">
         <v>5.5236</v>
@@ -1054,7 +1054,7 @@
         <v>4.0557</v>
       </c>
       <c r="D14" t="n">
-        <v>1.776</v>
+        <v>1.7231</v>
       </c>
       <c r="E14" t="n">
         <v>5.4394</v>
@@ -1100,7 +1100,7 @@
         <v>3.9764</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7331</v>
+        <v>1.6808</v>
       </c>
       <c r="E15" t="n">
         <v>5.333</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.3273</v>
+        <v>5.2842</v>
       </c>
       <c r="C16" t="n">
-        <v>3.9721</v>
+        <v>3.94</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7307</v>
+        <v>1.6613</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3273</v>
+        <v>5.2842</v>
       </c>
       <c r="F16" t="n">
-        <v>5.3273</v>
+        <v>5.2842</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>6.0501</v>
+        <v>5.9826</v>
       </c>
       <c r="I16" t="n">
         <v>6.1349</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.2084</v>
+        <v>5.1944</v>
       </c>
       <c r="C17" t="n">
-        <v>3.8835</v>
+        <v>3.873</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6827</v>
+        <v>1.6255</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2084</v>
+        <v>5.1944</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2084</v>
+        <v>5.1944</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8636</v>
+        <v>5.8418</v>
       </c>
       <c r="I17" t="n">
         <v>5.8909</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.9993</v>
+        <v>4.973</v>
       </c>
       <c r="C18" t="n">
-        <v>3.7275</v>
+        <v>3.7079</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5982</v>
+        <v>1.5373</v>
       </c>
       <c r="E18" t="n">
-        <v>4.9993</v>
+        <v>4.973</v>
       </c>
       <c r="F18" t="n">
-        <v>4.9993</v>
+        <v>4.973</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.5359</v>
+        <v>5.4947</v>
       </c>
       <c r="I18" t="n">
         <v>5.5876</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6683</v>
+        <v>4.6208</v>
       </c>
       <c r="C19" t="n">
-        <v>3.4807</v>
+        <v>3.4453</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4645</v>
+        <v>1.397</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6683</v>
+        <v>4.6208</v>
       </c>
       <c r="F19" t="n">
-        <v>4.6683</v>
+        <v>4.6208</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.0168</v>
+        <v>4.9424</v>
       </c>
       <c r="I19" t="n">
         <v>5.1109</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.6475</v>
+        <v>4.5887</v>
       </c>
       <c r="C20" t="n">
-        <v>3.4652</v>
+        <v>3.4214</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4561</v>
+        <v>1.3842</v>
       </c>
       <c r="E20" t="n">
-        <v>4.6475</v>
+        <v>4.5887</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6475</v>
+        <v>4.5887</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9842</v>
+        <v>4.892</v>
       </c>
       <c r="I20" t="n">
         <v>5.1013</v>
@@ -1376,7 +1376,7 @@
         <v>3.4086</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4255</v>
+        <v>1.3774</v>
       </c>
       <c r="E21" t="n">
         <v>4.5716</v>
@@ -1422,7 +1422,7 @@
         <v>3.3834</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4118</v>
+        <v>1.3639</v>
       </c>
       <c r="E22" t="n">
         <v>4.5377</v>
@@ -1468,7 +1468,7 @@
         <v>3.2076</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3165</v>
+        <v>1.27</v>
       </c>
       <c r="E23" t="n">
         <v>4.3019</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.175</v>
+        <v>4.1349</v>
       </c>
       <c r="C24" t="n">
-        <v>3.1129</v>
+        <v>3.083</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2652</v>
+        <v>1.2034</v>
       </c>
       <c r="E24" t="n">
-        <v>4.175</v>
+        <v>4.1349</v>
       </c>
       <c r="F24" t="n">
-        <v>4.175</v>
+        <v>4.1349</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2434</v>
+        <v>4.1804</v>
       </c>
       <c r="I24" t="n">
         <v>4.323</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.1062</v>
+        <v>4.0866</v>
       </c>
       <c r="C25" t="n">
-        <v>3.0616</v>
+        <v>3.047</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2375</v>
+        <v>1.1842</v>
       </c>
       <c r="E25" t="n">
-        <v>4.1062</v>
+        <v>4.0866</v>
       </c>
       <c r="F25" t="n">
-        <v>4.1062</v>
+        <v>4.0866</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1355</v>
+        <v>4.1047</v>
       </c>
       <c r="I25" t="n">
         <v>4.1741</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.0856</v>
+        <v>4.0715</v>
       </c>
       <c r="C26" t="n">
-        <v>3.0463</v>
+        <v>3.0358</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2291</v>
+        <v>1.1782</v>
       </c>
       <c r="E26" t="n">
-        <v>4.0856</v>
+        <v>4.0715</v>
       </c>
       <c r="F26" t="n">
-        <v>5.0856</v>
+        <v>0.2065</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>3.865</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6711</v>
+        <v>0.2065</v>
       </c>
       <c r="I26" t="n">
-        <v>5.8043</v>
+        <v>0.2065</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>3.865</v>
       </c>
       <c r="K26" t="n">
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>242</v>
       </c>
       <c r="M26" t="n">
-        <v>4.8043</v>
+        <v>4.0715</v>
       </c>
       <c r="N26" t="n">
-        <v>364</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.0715</v>
+        <v>4.0186</v>
       </c>
       <c r="C27" t="n">
-        <v>3.0358</v>
+        <v>2.9963</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2234</v>
+        <v>1.1571</v>
       </c>
       <c r="E27" t="n">
-        <v>4.0715</v>
+        <v>4.0186</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2065</v>
+        <v>5.0186</v>
       </c>
       <c r="G27" t="n">
-        <v>3.865</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2065</v>
+        <v>5.5661</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2065</v>
+        <v>5.8043</v>
       </c>
       <c r="J27" t="n">
-        <v>3.865</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>213</v>
+        <v>324</v>
       </c>
       <c r="L27" t="n">
-        <v>242</v>
+        <v>40</v>
       </c>
       <c r="M27" t="n">
-        <v>4.0715</v>
+        <v>4.8043</v>
       </c>
       <c r="N27" t="n">
-        <v>455</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.0596</v>
+        <v>4.0171</v>
       </c>
       <c r="C28" t="n">
-        <v>3.0269</v>
+        <v>2.9952</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2186</v>
+        <v>1.1565</v>
       </c>
       <c r="E28" t="n">
-        <v>4.0596</v>
+        <v>4.0171</v>
       </c>
       <c r="F28" t="n">
-        <v>4.0596</v>
+        <v>4.0171</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.0624</v>
+        <v>4.0171</v>
       </c>
       <c r="I28" t="n">
         <v>4.1194</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.0131</v>
+        <v>3.9536</v>
       </c>
       <c r="C29" t="n">
-        <v>2.9922</v>
+        <v>2.9479</v>
       </c>
       <c r="D29" t="n">
-        <v>1.1998</v>
+        <v>1.1312</v>
       </c>
       <c r="E29" t="n">
-        <v>4.0131</v>
+        <v>3.9536</v>
       </c>
       <c r="F29" t="n">
-        <v>4.0131</v>
+        <v>3.9536</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.0131</v>
+        <v>3.9536</v>
       </c>
       <c r="I29" t="n">
         <v>4.0884</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.9436</v>
+        <v>3.8956</v>
       </c>
       <c r="C30" t="n">
-        <v>2.9404</v>
+        <v>2.9046</v>
       </c>
       <c r="D30" t="n">
-        <v>1.1718</v>
+        <v>1.1081</v>
       </c>
       <c r="E30" t="n">
-        <v>3.9436</v>
+        <v>3.8956</v>
       </c>
       <c r="F30" t="n">
-        <v>3.9436</v>
+        <v>3.8956</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9436</v>
+        <v>3.8956</v>
       </c>
       <c r="I30" t="n">
-        <v>4.0362</v>
+        <v>3.8956</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>405</v>
+        <v>235</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.0362</v>
+        <v>3.8956</v>
       </c>
       <c r="N30" t="n">
-        <v>405</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.8956</v>
+        <v>3.8706</v>
       </c>
       <c r="C31" t="n">
-        <v>2.9046</v>
+        <v>2.886</v>
       </c>
       <c r="D31" t="n">
-        <v>1.1524</v>
+        <v>1.0981</v>
       </c>
       <c r="E31" t="n">
-        <v>3.8956</v>
+        <v>3.8706</v>
       </c>
       <c r="F31" t="n">
-        <v>3.8956</v>
+        <v>3.8706</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.8956</v>
+        <v>3.8706</v>
       </c>
       <c r="I31" t="n">
-        <v>3.8956</v>
+        <v>4.0362</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8956</v>
+        <v>4.0362</v>
       </c>
       <c r="N31" t="n">
-        <v>235</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>2.8775</v>
       </c>
       <c r="D32" t="n">
-        <v>1.1377</v>
+        <v>1.0936</v>
       </c>
       <c r="E32" t="n">
         <v>3.8593</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.8563</v>
+        <v>3.8192</v>
       </c>
       <c r="C33" t="n">
-        <v>2.8753</v>
+        <v>2.8476</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1365</v>
+        <v>1.0777</v>
       </c>
       <c r="E33" t="n">
-        <v>3.8563</v>
+        <v>3.8192</v>
       </c>
       <c r="F33" t="n">
-        <v>3.8563</v>
+        <v>3.0333</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.7859</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8563</v>
+        <v>3.0333</v>
       </c>
       <c r="I33" t="n">
-        <v>3.9469</v>
+        <v>3.0333</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7859</v>
       </c>
       <c r="K33" t="n">
-        <v>405</v>
+        <v>143</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9469</v>
+        <v>3.8192</v>
       </c>
       <c r="N33" t="n">
-        <v>405</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.8229</v>
+        <v>3.8044</v>
       </c>
       <c r="C34" t="n">
-        <v>2.8504</v>
+        <v>2.8366</v>
       </c>
       <c r="D34" t="n">
-        <v>1.123</v>
+        <v>1.0718</v>
       </c>
       <c r="E34" t="n">
-        <v>3.8229</v>
+        <v>3.8044</v>
       </c>
       <c r="F34" t="n">
-        <v>3.8229</v>
+        <v>3.4005</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.4039</v>
       </c>
       <c r="H34" t="n">
-        <v>3.8229</v>
+        <v>3.4005</v>
       </c>
       <c r="I34" t="n">
-        <v>3.8586</v>
+        <v>3.4291</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.4039</v>
       </c>
       <c r="K34" t="n">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8586</v>
+        <v>3.833</v>
       </c>
       <c r="N34" t="n">
-        <v>281</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.8192</v>
+        <v>3.7944</v>
       </c>
       <c r="C35" t="n">
-        <v>2.8476</v>
+        <v>2.8292</v>
       </c>
       <c r="D35" t="n">
-        <v>1.1215</v>
+        <v>1.0678</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8192</v>
+        <v>3.7944</v>
       </c>
       <c r="F35" t="n">
-        <v>3.0333</v>
+        <v>3.7944</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7859</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.0333</v>
+        <v>3.7944</v>
       </c>
       <c r="I35" t="n">
-        <v>3.0333</v>
+        <v>3.8586</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7859</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>143</v>
+        <v>281</v>
       </c>
       <c r="L35" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8192</v>
+        <v>3.8586</v>
       </c>
       <c r="N35" t="n">
-        <v>233</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.8171</v>
+        <v>3.7849</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8461</v>
+        <v>2.8221</v>
       </c>
       <c r="D36" t="n">
-        <v>1.1207</v>
+        <v>1.064</v>
       </c>
       <c r="E36" t="n">
-        <v>3.8171</v>
+        <v>3.7849</v>
       </c>
       <c r="F36" t="n">
-        <v>3.4132</v>
+        <v>3.7849</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4039</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.4132</v>
+        <v>3.7849</v>
       </c>
       <c r="I36" t="n">
-        <v>3.4291</v>
+        <v>3.9469</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4039</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>181</v>
+        <v>405</v>
       </c>
       <c r="L36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.833</v>
+        <v>3.9469</v>
       </c>
       <c r="N36" t="n">
-        <v>231</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37">
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.7031</v>
+        <v>3.6919</v>
       </c>
       <c r="C37" t="n">
-        <v>2.7611</v>
+        <v>2.7527</v>
       </c>
       <c r="D37" t="n">
-        <v>1.0746</v>
+        <v>1.0269</v>
       </c>
       <c r="E37" t="n">
-        <v>3.7031</v>
+        <v>3.6919</v>
       </c>
       <c r="F37" t="n">
-        <v>4.4711</v>
+        <v>4.4599</v>
       </c>
       <c r="G37" t="n">
         <v>-0.768</v>
       </c>
       <c r="H37" t="n">
-        <v>4.7076</v>
+        <v>4.69</v>
       </c>
       <c r="I37" t="n">
         <v>4.7295</v>
@@ -2158,7 +2158,7 @@
         <v>2.6697</v>
       </c>
       <c r="D38" t="n">
-        <v>1.0251</v>
+        <v>0.9826</v>
       </c>
       <c r="E38" t="n">
         <v>3.5805</v>
@@ -2204,7 +2204,7 @@
         <v>2.5185</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9432</v>
+        <v>0.9018</v>
       </c>
       <c r="E39" t="n">
         <v>3.3778</v>
@@ -2250,7 +2250,7 @@
         <v>2.5006</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9335</v>
+        <v>0.8922</v>
       </c>
       <c r="E40" t="n">
         <v>3.3537</v>
@@ -2286,231 +2286,231 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.3169</v>
+        <v>3.2891</v>
       </c>
       <c r="C41" t="n">
-        <v>2.4731</v>
+        <v>2.4524</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9186</v>
+        <v>0.8665</v>
       </c>
       <c r="E41" t="n">
-        <v>3.3169</v>
+        <v>3.2891</v>
       </c>
       <c r="F41" t="n">
-        <v>3.3169</v>
+        <v>3.2891</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3.3169</v>
+        <v>3.2891</v>
       </c>
       <c r="I41" t="n">
-        <v>3.3948</v>
+        <v>3.2891</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>405</v>
+        <v>209</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3948</v>
+        <v>3.2891</v>
       </c>
       <c r="N41" t="n">
-        <v>405</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.3011</v>
+        <v>3.2783</v>
       </c>
       <c r="C42" t="n">
-        <v>2.4613</v>
+        <v>2.4443</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9122</v>
+        <v>0.8622</v>
       </c>
       <c r="E42" t="n">
-        <v>3.3011</v>
+        <v>3.2783</v>
       </c>
       <c r="F42" t="n">
-        <v>3.3011</v>
+        <v>4.3696</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-1.0913</v>
       </c>
       <c r="H42" t="n">
-        <v>3.3011</v>
+        <v>4.5485</v>
       </c>
       <c r="I42" t="n">
-        <v>3.3787</v>
+        <v>4.5485</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-1.0913</v>
       </c>
       <c r="K42" t="n">
-        <v>374</v>
+        <v>213</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3787</v>
+        <v>3.4572</v>
       </c>
       <c r="N42" t="n">
-        <v>374</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.2891</v>
+        <v>3.2554</v>
       </c>
       <c r="C43" t="n">
-        <v>2.4524</v>
+        <v>2.4273</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9074</v>
+        <v>0.853</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2891</v>
+        <v>3.2554</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2891</v>
+        <v>3.2554</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2891</v>
+        <v>3.2554</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2891</v>
+        <v>3.3948</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>209</v>
+        <v>405</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2891</v>
+        <v>3.3948</v>
       </c>
       <c r="N43" t="n">
-        <v>209</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.2783</v>
+        <v>3.2521</v>
       </c>
       <c r="C44" t="n">
-        <v>2.4443</v>
+        <v>2.4248</v>
       </c>
       <c r="D44" t="n">
-        <v>0.903</v>
+        <v>0.8517</v>
       </c>
       <c r="E44" t="n">
-        <v>3.2783</v>
+        <v>3.2521</v>
       </c>
       <c r="F44" t="n">
-        <v>4.3696</v>
+        <v>3.2521</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>4.5485</v>
+        <v>3.2521</v>
       </c>
       <c r="I44" t="n">
-        <v>4.5485</v>
+        <v>3.2521</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>213</v>
+        <v>312</v>
       </c>
       <c r="L44" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4572</v>
+        <v>3.2521</v>
       </c>
       <c r="N44" t="n">
-        <v>455</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.2521</v>
+        <v>3.24</v>
       </c>
       <c r="C45" t="n">
-        <v>2.4248</v>
+        <v>2.4158</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8924</v>
+        <v>0.8469</v>
       </c>
       <c r="E45" t="n">
-        <v>3.2521</v>
+        <v>3.24</v>
       </c>
       <c r="F45" t="n">
-        <v>3.2521</v>
+        <v>3.24</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3.2521</v>
+        <v>3.24</v>
       </c>
       <c r="I45" t="n">
-        <v>3.2521</v>
+        <v>3.3787</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2521</v>
+        <v>3.3787</v>
       </c>
       <c r="N45" t="n">
-        <v>312</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46">
@@ -2526,7 +2526,7 @@
         <v>2.3348</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8437</v>
+        <v>0.8036</v>
       </c>
       <c r="E46" t="n">
         <v>3.1314</v>
@@ -2572,7 +2572,7 @@
         <v>2.2189</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7809</v>
+        <v>0.7417</v>
       </c>
       <c r="E47" t="n">
         <v>2.976</v>
@@ -2608,93 +2608,93 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.905</v>
+        <v>2.9002</v>
       </c>
       <c r="C48" t="n">
-        <v>2.166</v>
+        <v>2.1624</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7522</v>
+        <v>0.7115</v>
       </c>
       <c r="E48" t="n">
-        <v>2.905</v>
+        <v>2.9002</v>
       </c>
       <c r="F48" t="n">
-        <v>2.905</v>
+        <v>1.0357</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1.8645</v>
       </c>
       <c r="H48" t="n">
-        <v>2.905</v>
+        <v>1.0357</v>
       </c>
       <c r="I48" t="n">
-        <v>2.9321</v>
+        <v>1.0357</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1.8645</v>
       </c>
       <c r="K48" t="n">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9321</v>
+        <v>2.9002</v>
       </c>
       <c r="N48" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.9002</v>
+        <v>2.8833</v>
       </c>
       <c r="C49" t="n">
-        <v>2.1624</v>
+        <v>2.1498</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7503</v>
+        <v>0.7048</v>
       </c>
       <c r="E49" t="n">
-        <v>2.9002</v>
+        <v>2.8833</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0357</v>
+        <v>2.8833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.8645</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0357</v>
+        <v>2.8833</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0357</v>
+        <v>2.9321</v>
       </c>
       <c r="J49" t="n">
-        <v>1.8645</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="L49" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9002</v>
+        <v>2.9321</v>
       </c>
       <c r="N49" t="n">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50">
@@ -2710,7 +2710,7 @@
         <v>2.0988</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7158</v>
+        <v>0.6775</v>
       </c>
       <c r="E50" t="n">
         <v>2.8149</v>
@@ -2746,93 +2746,93 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.794</v>
+        <v>2.7801</v>
       </c>
       <c r="C51" t="n">
-        <v>2.0832</v>
+        <v>2.0729</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7074</v>
+        <v>0.6637</v>
       </c>
       <c r="E51" t="n">
-        <v>2.794</v>
+        <v>2.7801</v>
       </c>
       <c r="F51" t="n">
-        <v>2.794</v>
+        <v>2.7801</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.794</v>
+        <v>2.7801</v>
       </c>
       <c r="I51" t="n">
-        <v>2.82</v>
+        <v>2.7801</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.82</v>
+        <v>2.7801</v>
       </c>
       <c r="N51" t="n">
-        <v>281</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.7801</v>
+        <v>2.7732</v>
       </c>
       <c r="C52" t="n">
-        <v>2.0729</v>
+        <v>2.0677</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7017</v>
+        <v>0.6609</v>
       </c>
       <c r="E52" t="n">
-        <v>2.7801</v>
+        <v>2.7732</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7801</v>
+        <v>2.7732</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.7801</v>
+        <v>2.7732</v>
       </c>
       <c r="I52" t="n">
-        <v>2.7801</v>
+        <v>2.82</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.7801</v>
+        <v>2.82</v>
       </c>
       <c r="N52" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53">
@@ -2848,7 +2848,7 @@
         <v>2.0653</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6976</v>
+        <v>0.6596</v>
       </c>
       <c r="E53" t="n">
         <v>2.7699</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.6953</v>
+        <v>2.6848</v>
       </c>
       <c r="C54" t="n">
-        <v>2.0097</v>
+        <v>2.0018</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6675</v>
+        <v>0.6257</v>
       </c>
       <c r="E54" t="n">
-        <v>2.6953</v>
+        <v>2.6848</v>
       </c>
       <c r="F54" t="n">
-        <v>2.8293</v>
+        <v>2.8188</v>
       </c>
       <c r="G54" t="n">
         <v>-0.134</v>
       </c>
       <c r="H54" t="n">
-        <v>2.8293</v>
+        <v>2.8188</v>
       </c>
       <c r="I54" t="n">
         <v>2.8425</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.5539</v>
+        <v>2.5444</v>
       </c>
       <c r="C55" t="n">
-        <v>1.9042</v>
+        <v>1.8971</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5698</v>
       </c>
       <c r="E55" t="n">
-        <v>2.5539</v>
+        <v>2.5444</v>
       </c>
       <c r="F55" t="n">
-        <v>2.5539</v>
+        <v>2.5444</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2.5539</v>
+        <v>2.5444</v>
       </c>
       <c r="I55" t="n">
         <v>2.5658</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.4426</v>
+        <v>2.3974</v>
       </c>
       <c r="C56" t="n">
-        <v>1.8212</v>
+        <v>1.7875</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5654</v>
+        <v>0.5112</v>
       </c>
       <c r="E56" t="n">
-        <v>2.4426</v>
+        <v>2.3974</v>
       </c>
       <c r="F56" t="n">
-        <v>2.4426</v>
+        <v>2.3974</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2.4426</v>
+        <v>2.3974</v>
       </c>
       <c r="I56" t="n">
         <v>2.5</v>
@@ -3032,7 +3032,7 @@
         <v>1.7789</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5424</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="E57" t="n">
         <v>2.3858</v>
@@ -3078,7 +3078,7 @@
         <v>1.6946</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4968</v>
+        <v>0.4615</v>
       </c>
       <c r="E58" t="n">
         <v>2.2727</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.1976</v>
+        <v>2.165</v>
       </c>
       <c r="C59" t="n">
-        <v>1.6386</v>
+        <v>1.6143</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4664</v>
+        <v>0.4186</v>
       </c>
       <c r="E59" t="n">
-        <v>2.1976</v>
+        <v>2.165</v>
       </c>
       <c r="F59" t="n">
-        <v>2.1976</v>
+        <v>2.165</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2.1976</v>
+        <v>2.165</v>
       </c>
       <c r="I59" t="n">
         <v>2.2388</v>
@@ -3170,7 +3170,7 @@
         <v>1.579</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4341</v>
+        <v>0.3998</v>
       </c>
       <c r="E60" t="n">
         <v>2.1177</v>
@@ -3216,7 +3216,7 @@
         <v>1.5205</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4024</v>
+        <v>0.3685</v>
       </c>
       <c r="E61" t="n">
         <v>2.0392</v>
@@ -3262,7 +3262,7 @@
         <v>1.517</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4006</v>
+        <v>0.3667</v>
       </c>
       <c r="E62" t="n">
         <v>2.0346</v>
@@ -3308,7 +3308,7 @@
         <v>1.4443</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3611</v>
+        <v>0.3278</v>
       </c>
       <c r="E63" t="n">
         <v>1.937</v>
@@ -3354,7 +3354,7 @@
         <v>1.4372</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3573</v>
+        <v>0.324</v>
       </c>
       <c r="E64" t="n">
         <v>1.9276</v>
@@ -3390,139 +3390,139 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.8671</v>
+        <v>1.8599</v>
       </c>
       <c r="C65" t="n">
-        <v>1.3921</v>
+        <v>1.3868</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3329</v>
+        <v>0.2971</v>
       </c>
       <c r="E65" t="n">
-        <v>1.8671</v>
+        <v>1.8599</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8671</v>
+        <v>2.8599</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" t="n">
-        <v>1.8671</v>
+        <v>2.8599</v>
       </c>
       <c r="I65" t="n">
-        <v>1.8845</v>
+        <v>2.8599</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K65" t="n">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M65" t="n">
-        <v>1.8845</v>
+        <v>1.8599</v>
       </c>
       <c r="N65" t="n">
-        <v>281</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.8599</v>
+        <v>1.854</v>
       </c>
       <c r="C66" t="n">
-        <v>1.3868</v>
+        <v>1.3824</v>
       </c>
       <c r="D66" t="n">
-        <v>0.33</v>
+        <v>0.2947</v>
       </c>
       <c r="E66" t="n">
-        <v>1.8599</v>
+        <v>1.854</v>
       </c>
       <c r="F66" t="n">
-        <v>2.8599</v>
+        <v>2.4143</v>
       </c>
       <c r="G66" t="n">
-        <v>-1</v>
+        <v>-0.5603</v>
       </c>
       <c r="H66" t="n">
-        <v>2.8599</v>
+        <v>2.4143</v>
       </c>
       <c r="I66" t="n">
-        <v>2.8599</v>
+        <v>2.4143</v>
       </c>
       <c r="J66" t="n">
-        <v>-1</v>
+        <v>-0.5603</v>
       </c>
       <c r="K66" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="L66" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="M66" t="n">
-        <v>1.8599</v>
+        <v>1.854</v>
       </c>
       <c r="N66" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.854</v>
+        <v>1.8532</v>
       </c>
       <c r="C67" t="n">
-        <v>1.3824</v>
+        <v>1.3818</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3276</v>
+        <v>0.2944</v>
       </c>
       <c r="E67" t="n">
-        <v>1.854</v>
+        <v>1.8532</v>
       </c>
       <c r="F67" t="n">
-        <v>2.4143</v>
+        <v>1.8532</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.5603</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.4143</v>
+        <v>1.8532</v>
       </c>
       <c r="I67" t="n">
-        <v>2.4143</v>
+        <v>1.8845</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.5603</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="L67" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1.854</v>
+        <v>1.8845</v>
       </c>
       <c r="N67" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68">
@@ -3538,7 +3538,7 @@
         <v>1.3414</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3054</v>
+        <v>0.2728</v>
       </c>
       <c r="E68" t="n">
         <v>1.799</v>
@@ -3584,7 +3584,7 @@
         <v>1.3127</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2898</v>
+        <v>0.2575</v>
       </c>
       <c r="E69" t="n">
         <v>1.7605</v>
@@ -3630,7 +3630,7 @@
         <v>1.2673</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2653</v>
+        <v>0.2333</v>
       </c>
       <c r="E70" t="n">
         <v>1.6997</v>
@@ -3676,7 +3676,7 @@
         <v>1.2473</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2544</v>
+        <v>0.2225</v>
       </c>
       <c r="E71" t="n">
         <v>1.6728</v>
@@ -3722,7 +3722,7 @@
         <v>1.2307</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2454</v>
+        <v>0.2137</v>
       </c>
       <c r="E72" t="n">
         <v>1.6506</v>
@@ -3768,7 +3768,7 @@
         <v>1.2126</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2356</v>
+        <v>0.204</v>
       </c>
       <c r="E73" t="n">
         <v>1.6263</v>
@@ -3814,7 +3814,7 @@
         <v>1.1201</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1855</v>
+        <v>0.1546</v>
       </c>
       <c r="E74" t="n">
         <v>1.5023</v>
@@ -3860,7 +3860,7 @@
         <v>1.0773</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1623</v>
+        <v>0.1317</v>
       </c>
       <c r="E75" t="n">
         <v>1.4448</v>
@@ -3906,7 +3906,7 @@
         <v>1.0497</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1474</v>
+        <v>0.117</v>
       </c>
       <c r="E76" t="n">
         <v>1.4078</v>
@@ -3952,7 +3952,7 @@
         <v>1.0078</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1247</v>
+        <v>0.0946</v>
       </c>
       <c r="E77" t="n">
         <v>1.3516</v>
@@ -3998,7 +3998,7 @@
         <v>0.971</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1047</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="E78" t="n">
         <v>1.3023</v>
@@ -4044,7 +4044,7 @@
         <v>0.9577</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0975</v>
+        <v>0.0678</v>
       </c>
       <c r="E79" t="n">
         <v>1.2844</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.2645</v>
+        <v>1.2504</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9428</v>
+        <v>0.9323</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0895</v>
+        <v>0.0542</v>
       </c>
       <c r="E80" t="n">
-        <v>1.2645</v>
+        <v>1.2504</v>
       </c>
       <c r="F80" t="n">
-        <v>1.2645</v>
+        <v>1.2504</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1.2645</v>
+        <v>1.2504</v>
       </c>
       <c r="I80" t="n">
         <v>1.2823</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.2561</v>
+        <v>1.2468</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9366</v>
+        <v>0.9296</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0861</v>
+        <v>0.0528</v>
       </c>
       <c r="E81" t="n">
-        <v>1.2561</v>
+        <v>1.2468</v>
       </c>
       <c r="F81" t="n">
-        <v>1.2561</v>
+        <v>1.2468</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1.2561</v>
+        <v>1.2468</v>
       </c>
       <c r="I81" t="n">
         <v>1.2679</v>
@@ -4182,7 +4182,7 @@
         <v>0.8877</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0596</v>
+        <v>0.0304</v>
       </c>
       <c r="E82" t="n">
         <v>1.1906</v>
@@ -4218,93 +4218,93 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.0747</v>
+        <v>1.0604</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8013</v>
+        <v>0.7906</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0128</v>
+        <v>-0.0214</v>
       </c>
       <c r="E83" t="n">
-        <v>1.0747</v>
+        <v>1.0604</v>
       </c>
       <c r="F83" t="n">
-        <v>1.0747</v>
+        <v>1.0604</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1.0747</v>
+        <v>1.0604</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0999</v>
+        <v>1.0604</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>374</v>
+        <v>231</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1.0999</v>
+        <v>1.0604</v>
       </c>
       <c r="N83" t="n">
-        <v>374</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.0604</v>
+        <v>1.0548</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7906</v>
+        <v>0.7865</v>
       </c>
       <c r="D84" t="n">
-        <v>0.007</v>
+        <v>-0.0237</v>
       </c>
       <c r="E84" t="n">
-        <v>1.0604</v>
+        <v>1.0548</v>
       </c>
       <c r="F84" t="n">
-        <v>1.0604</v>
+        <v>1.0548</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1.0604</v>
+        <v>1.0548</v>
       </c>
       <c r="I84" t="n">
-        <v>1.0604</v>
+        <v>1.0999</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>231</v>
+        <v>374</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1.0604</v>
+        <v>1.0999</v>
       </c>
       <c r="N84" t="n">
-        <v>231</v>
+        <v>374</v>
       </c>
     </row>
     <row r="85">
@@ -4320,7 +4320,7 @@
         <v>0.7397</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.0206</v>
+        <v>-0.0487</v>
       </c>
       <c r="E85" t="n">
         <v>0.9921</v>
@@ -4366,7 +4366,7 @@
         <v>0.6938</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.0455</v>
+        <v>-0.0732</v>
       </c>
       <c r="E86" t="n">
         <v>0.9305</v>
@@ -4412,7 +4412,7 @@
         <v>0.6241</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0832</v>
+        <v>-0.1104</v>
       </c>
       <c r="E87" t="n">
         <v>0.837</v>
@@ -4448,93 +4448,93 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7724</v>
+        <v>0.7718</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5759</v>
+        <v>0.5755</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1093</v>
+        <v>-0.1364</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7724</v>
+        <v>0.7718</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7724</v>
+        <v>0.7718</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.7724</v>
+        <v>0.7718</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7869</v>
+        <v>0.7718</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>385</v>
+        <v>265</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7869</v>
+        <v>0.7718</v>
       </c>
       <c r="N88" t="n">
-        <v>385</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7718</v>
+        <v>0.7609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5755</v>
+        <v>0.5673</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1096</v>
+        <v>-0.1408</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7718</v>
+        <v>0.7609</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7718</v>
+        <v>0.7609</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7718</v>
+        <v>0.7609</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7718</v>
+        <v>0.7869</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0.7718</v>
+        <v>0.7869</v>
       </c>
       <c r="N89" t="n">
-        <v>265</v>
+        <v>385</v>
       </c>
     </row>
     <row r="90">
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.705</v>
+        <v>0.6998</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5218</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1366</v>
+        <v>-0.1651</v>
       </c>
       <c r="E90" t="n">
-        <v>0.705</v>
+        <v>0.6998</v>
       </c>
       <c r="F90" t="n">
-        <v>0.705</v>
+        <v>0.6998</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.705</v>
+        <v>0.6998</v>
       </c>
       <c r="I90" t="n">
         <v>0.7116</v>
@@ -4596,7 +4596,7 @@
         <v>0.453</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.1759</v>
+        <v>-0.2019</v>
       </c>
       <c r="E91" t="n">
         <v>0.6075</v>
@@ -4642,7 +4642,7 @@
         <v>0.45</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.1776</v>
+        <v>-0.2035</v>
       </c>
       <c r="E92" t="n">
         <v>0.6035</v>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5904</v>
+        <v>0.5866</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4402</v>
+        <v>0.4374</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.1829</v>
+        <v>-0.2102</v>
       </c>
       <c r="E93" t="n">
-        <v>0.5904</v>
+        <v>0.5866</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9993</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G93" t="n">
         <v>-0.4089</v>
       </c>
       <c r="H93" t="n">
-        <v>0.9993</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="I93" t="n">
         <v>1.0039</v>
@@ -4734,7 +4734,7 @@
         <v>0.3804</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.2153</v>
+        <v>-0.2406</v>
       </c>
       <c r="E94" t="n">
         <v>0.5102</v>
@@ -4780,7 +4780,7 @@
         <v>0.3425</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.2358</v>
+        <v>-0.2609</v>
       </c>
       <c r="E95" t="n">
         <v>0.4593</v>
@@ -4826,7 +4826,7 @@
         <v>0.2825</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.2683</v>
+        <v>-0.293</v>
       </c>
       <c r="E96" t="n">
         <v>0.3789</v>
@@ -4872,7 +4872,7 @@
         <v>0.2569</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.2822</v>
+        <v>-0.3066</v>
       </c>
       <c r="E97" t="n">
         <v>0.3446</v>
@@ -4918,7 +4918,7 @@
         <v>0.1891</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.3189</v>
+        <v>-0.3429</v>
       </c>
       <c r="E98" t="n">
         <v>0.2536</v>
@@ -4964,7 +4964,7 @@
         <v>0.1837</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.3218</v>
+        <v>-0.3457</v>
       </c>
       <c r="E99" t="n">
         <v>0.2464</v>
@@ -5004,25 +5004,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.1905</v>
+        <v>0.1856</v>
       </c>
       <c r="C100" t="n">
-        <v>0.142</v>
+        <v>0.1384</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.3444</v>
+        <v>-0.37</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1905</v>
+        <v>0.1856</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2693</v>
+        <v>0.2644</v>
       </c>
       <c r="G100" t="n">
         <v>-0.0788</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2693</v>
+        <v>0.2644</v>
       </c>
       <c r="I100" t="n">
         <v>0.2757</v>
@@ -5056,7 +5056,7 @@
         <v>0.1036</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.3652</v>
+        <v>-0.3886</v>
       </c>
       <c r="E101" t="n">
         <v>0.1389</v>
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.0336</v>
+        <v>-0.033</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.0251</v>
+        <v>-0.0246</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.4349</v>
+        <v>-0.4571</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.0336</v>
+        <v>-0.033</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.0336</v>
+        <v>-0.033</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.0336</v>
+        <v>-0.033</v>
       </c>
       <c r="I102" t="n">
         <v>-0.0344</v>
@@ -5148,7 +5148,7 @@
         <v>-0.055</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.4512</v>
+        <v>-0.4733</v>
       </c>
       <c r="E103" t="n">
         <v>-0.0738</v>
@@ -5188,25 +5188,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.1054</v>
+        <v>-0.1042</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.0786</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.4639</v>
+        <v>-0.4854</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.1054</v>
+        <v>-0.1042</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.1054</v>
+        <v>-0.1042</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.1054</v>
+        <v>-0.1042</v>
       </c>
       <c r="I104" t="n">
         <v>-0.1069</v>
@@ -5240,7 +5240,7 @@
         <v>-0.0818</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.4657</v>
+        <v>-0.4876</v>
       </c>
       <c r="E105" t="n">
         <v>-0.1097</v>
@@ -5286,7 +5286,7 @@
         <v>-0.166</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.5113</v>
+        <v>-0.5326</v>
       </c>
       <c r="E106" t="n">
         <v>-0.2227</v>
@@ -5332,7 +5332,7 @@
         <v>-0.2229</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.5421</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="E107" t="n">
         <v>-0.2989</v>
@@ -5378,7 +5378,7 @@
         <v>-0.2405</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.5517</v>
+        <v>-0.5724</v>
       </c>
       <c r="E108" t="n">
         <v>-0.3226</v>
@@ -5418,25 +5418,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.357</v>
+        <v>-0.3557</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2662</v>
+        <v>-0.2652</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.5656</v>
+        <v>-0.5856</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.357</v>
+        <v>-0.3557</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.357</v>
+        <v>-0.3557</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.357</v>
+        <v>-0.3557</v>
       </c>
       <c r="I109" t="n">
         <v>-0.3586</v>
@@ -5470,7 +5470,7 @@
         <v>-0.2751</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.5704</v>
+        <v>-0.5909</v>
       </c>
       <c r="E110" t="n">
         <v>-0.3689</v>
@@ -5510,25 +5510,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-0.3911</v>
+        <v>-0.3882</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2916</v>
+        <v>-0.2894</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5794</v>
+        <v>-0.5986</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.3911</v>
+        <v>-0.3882</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.3911</v>
+        <v>-0.3882</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.3911</v>
+        <v>-0.3882</v>
       </c>
       <c r="I111" t="n">
         <v>-0.3948</v>
@@ -5562,7 +5562,7 @@
         <v>-0.3003</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.584</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="E112" t="n">
         <v>-0.4027</v>
@@ -5608,7 +5608,7 @@
         <v>-0.3584</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.6156</v>
+        <v>-0.6354</v>
       </c>
       <c r="E113" t="n">
         <v>-0.4807</v>
@@ -5654,7 +5654,7 @@
         <v>-0.385</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.63</v>
+        <v>-0.6496</v>
       </c>
       <c r="E114" t="n">
         <v>-0.5164</v>
@@ -5700,7 +5700,7 @@
         <v>-0.4641</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.6728</v>
+        <v>-0.6919</v>
       </c>
       <c r="E115" t="n">
         <v>-0.6225000000000001</v>
@@ -5746,7 +5746,7 @@
         <v>-0.4691</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.6755</v>
+        <v>-0.6945</v>
       </c>
       <c r="E116" t="n">
         <v>-0.6291</v>
@@ -5792,7 +5792,7 @@
         <v>-0.506</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6955</v>
+        <v>-0.7143</v>
       </c>
       <c r="E117" t="n">
         <v>-0.6786</v>
@@ -5838,7 +5838,7 @@
         <v>-0.5223</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.7043</v>
+        <v>-0.723</v>
       </c>
       <c r="E118" t="n">
         <v>-0.7005</v>
@@ -5884,7 +5884,7 @@
         <v>-0.5488</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.7187</v>
+        <v>-0.7371</v>
       </c>
       <c r="E119" t="n">
         <v>-0.736</v>
@@ -5930,7 +5930,7 @@
         <v>-0.5566</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.7229</v>
+        <v>-0.7413</v>
       </c>
       <c r="E120" t="n">
         <v>-0.7465000000000001</v>
@@ -5976,7 +5976,7 @@
         <v>-0.5623</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.726</v>
+        <v>-0.7443</v>
       </c>
       <c r="E121" t="n">
         <v>-0.7541</v>
@@ -6022,7 +6022,7 @@
         <v>-0.6132</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.7536</v>
+        <v>-0.7716</v>
       </c>
       <c r="E122" t="n">
         <v>-0.8224</v>
@@ -6068,7 +6068,7 @@
         <v>-0.6536999999999999</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.7755</v>
+        <v>-0.7932</v>
       </c>
       <c r="E123" t="n">
         <v>-0.8767</v>
@@ -6114,7 +6114,7 @@
         <v>-0.7577</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.8319</v>
+        <v>-0.8488</v>
       </c>
       <c r="E124" t="n">
         <v>-1.0162</v>
@@ -6154,25 +6154,25 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-1.1878</v>
+        <v>-1.1852</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.8837</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.9012</v>
+        <v>-0.9161</v>
       </c>
       <c r="E125" t="n">
-        <v>-1.1878</v>
+        <v>-1.1852</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.7025</v>
       </c>
       <c r="G125" t="n">
         <v>-0.4827</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.7025</v>
       </c>
       <c r="I125" t="n">
         <v>-0.7084</v>
@@ -6206,7 +6206,7 @@
         <v>-0.9371</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.9291</v>
+        <v>-0.9446</v>
       </c>
       <c r="E126" t="n">
         <v>-1.2568</v>
@@ -6252,7 +6252,7 @@
         <v>-0.9659</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.9447</v>
+        <v>-0.96</v>
       </c>
       <c r="E127" t="n">
         <v>-1.2955</v>
@@ -6298,7 +6298,7 @@
         <v>-0.9668</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.9452</v>
+        <v>-0.9605</v>
       </c>
       <c r="E128" t="n">
         <v>-1.2967</v>
@@ -6344,7 +6344,7 @@
         <v>-0.9893999999999999</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.9574</v>
+        <v>-0.9725</v>
       </c>
       <c r="E129" t="n">
         <v>-1.3269</v>
@@ -6390,7 +6390,7 @@
         <v>-1.0565</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.9938</v>
+        <v>-1.0084</v>
       </c>
       <c r="E130" t="n">
         <v>-1.417</v>
@@ -6436,7 +6436,7 @@
         <v>-1.1908</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.0666</v>
+        <v>-1.0802</v>
       </c>
       <c r="E131" t="n">
         <v>-1.5971</v>
@@ -6482,7 +6482,7 @@
         <v>-1.2175</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.081</v>
+        <v>-1.0945</v>
       </c>
       <c r="E132" t="n">
         <v>-1.6329</v>
@@ -6522,25 +6522,25 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-1.6546</v>
+        <v>-1.6484</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.2337</v>
+        <v>-1.2291</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.0898</v>
+        <v>-1.1006</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.6546</v>
+        <v>-1.6484</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.6546</v>
+        <v>-1.6484</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.6546</v>
+        <v>-1.6484</v>
       </c>
       <c r="I133" t="n">
         <v>-1.6623</v>
@@ -6574,7 +6574,7 @@
         <v>-1.2406</v>
       </c>
       <c r="D134" t="n">
-        <v>-1.0935</v>
+        <v>-1.1068</v>
       </c>
       <c r="E134" t="n">
         <v>-1.6638</v>
@@ -6620,7 +6620,7 @@
         <v>-1.2746</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.1119</v>
+        <v>-1.1249</v>
       </c>
       <c r="E135" t="n">
         <v>-1.7094</v>
@@ -6666,7 +6666,7 @@
         <v>-1.2787</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.1142</v>
+        <v>-1.1272</v>
       </c>
       <c r="E136" t="n">
         <v>-1.715</v>
@@ -6712,7 +6712,7 @@
         <v>-1.364</v>
       </c>
       <c r="D137" t="n">
-        <v>-1.1604</v>
+        <v>-1.1727</v>
       </c>
       <c r="E137" t="n">
         <v>-1.8294</v>
@@ -6758,7 +6758,7 @@
         <v>-1.4246</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.1932</v>
+        <v>-1.2051</v>
       </c>
       <c r="E138" t="n">
         <v>-1.9106</v>
@@ -6798,25 +6798,25 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-1.9538</v>
+        <v>-1.9176</v>
       </c>
       <c r="C139" t="n">
-        <v>-1.4568</v>
+        <v>-1.4298</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.2107</v>
+        <v>-1.2079</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.9538</v>
+        <v>-1.9176</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.9538</v>
+        <v>-1.9176</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.9538</v>
+        <v>-1.9176</v>
       </c>
       <c r="I139" t="n">
         <v>-1.9997</v>
@@ -6850,7 +6850,7 @@
         <v>-1.5584</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.2657</v>
+        <v>-1.2766</v>
       </c>
       <c r="E140" t="n">
         <v>-2.0901</v>
@@ -6896,7 +6896,7 @@
         <v>-1.6449</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.3126</v>
+        <v>-1.3228</v>
       </c>
       <c r="E141" t="n">
         <v>-2.2061</v>
@@ -6942,7 +6942,7 @@
         <v>-1.6559</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.3185</v>
+        <v>-1.3287</v>
       </c>
       <c r="E142" t="n">
         <v>-2.2208</v>
@@ -6988,7 +6988,7 @@
         <v>-1.6623</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.322</v>
+        <v>-1.3321</v>
       </c>
       <c r="E143" t="n">
         <v>-2.2294</v>
@@ -7034,7 +7034,7 @@
         <v>-1.7957</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.3943</v>
+        <v>-1.4034</v>
       </c>
       <c r="E144" t="n">
         <v>-2.4083</v>
@@ -7080,7 +7080,7 @@
         <v>-1.832</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.414</v>
+        <v>-1.4228</v>
       </c>
       <c r="E145" t="n">
         <v>-2.4571</v>
@@ -7126,7 +7126,7 @@
         <v>-1.8436</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.4202</v>
+        <v>-1.429</v>
       </c>
       <c r="E146" t="n">
         <v>-2.4726</v>
@@ -7172,7 +7172,7 @@
         <v>-1.8611</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.4297</v>
+        <v>-1.4383</v>
       </c>
       <c r="E147" t="n">
         <v>-2.496</v>
@@ -7208,139 +7208,139 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-2.6837</v>
+        <v>-2.6733</v>
       </c>
       <c r="C148" t="n">
-        <v>-2.001</v>
+        <v>-1.9932</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.5055</v>
+        <v>-1.509</v>
       </c>
       <c r="E148" t="n">
-        <v>-2.6837</v>
+        <v>-2.6733</v>
       </c>
       <c r="F148" t="n">
-        <v>-2.6837</v>
+        <v>-2.6733</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>-2.6837</v>
+        <v>-2.6733</v>
       </c>
       <c r="I148" t="n">
-        <v>-2.6837</v>
+        <v>-2.7185</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>-2.6837</v>
+        <v>-2.7185</v>
       </c>
       <c r="N148" t="n">
-        <v>209</v>
+        <v>289</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="C149" t="n">
-        <v>-2.0067</v>
+        <v>-2.001</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.5086</v>
+        <v>-1.5131</v>
       </c>
       <c r="E149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="F149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="I149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>-2.6913</v>
+        <v>-2.6837</v>
       </c>
       <c r="N149" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-2.6934</v>
+        <v>-2.6913</v>
       </c>
       <c r="C150" t="n">
-        <v>-2.0082</v>
+        <v>-2.0067</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.5094</v>
+        <v>-1.5161</v>
       </c>
       <c r="E150" t="n">
-        <v>-2.6934</v>
+        <v>-2.6913</v>
       </c>
       <c r="F150" t="n">
-        <v>-2.6934</v>
+        <v>-2.6913</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>-2.6934</v>
+        <v>-2.6913</v>
       </c>
       <c r="I150" t="n">
-        <v>-2.7185</v>
+        <v>-2.6913</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>-2.7185</v>
+        <v>-2.6913</v>
       </c>
       <c r="N150" t="n">
-        <v>289</v>
+        <v>190</v>
       </c>
     </row>
     <row r="151">
@@ -7356,7 +7356,7 @@
         <v>-2.0421</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.5278</v>
+        <v>-1.535</v>
       </c>
       <c r="E151" t="n">
         <v>-2.7388</v>
@@ -7402,7 +7402,7 @@
         <v>-2.1166</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.5681</v>
+        <v>-1.5748</v>
       </c>
       <c r="E152" t="n">
         <v>-2.8387</v>
@@ -7448,7 +7448,7 @@
         <v>-2.2368</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.6333</v>
+        <v>-1.6391</v>
       </c>
       <c r="E153" t="n">
         <v>-3</v>
@@ -7494,7 +7494,7 @@
         <v>-2.294</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.6643</v>
+        <v>-1.6697</v>
       </c>
       <c r="E154" t="n">
         <v>-3.0767</v>
@@ -7540,7 +7540,7 @@
         <v>-2.3106</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.6732</v>
+        <v>-1.6785</v>
       </c>
       <c r="E155" t="n">
         <v>-3.0989</v>
@@ -7586,7 +7586,7 @@
         <v>-2.3857</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.714</v>
+        <v>-1.7187</v>
       </c>
       <c r="E156" t="n">
         <v>-3.1997</v>
@@ -7626,25 +7626,25 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-3.674</v>
+        <v>-3.633</v>
       </c>
       <c r="C157" t="n">
-        <v>-2.7394</v>
+        <v>-2.7088</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.9056</v>
+        <v>-1.8913</v>
       </c>
       <c r="E157" t="n">
-        <v>-3.674</v>
+        <v>-3.633</v>
       </c>
       <c r="F157" t="n">
-        <v>-3.674</v>
+        <v>-3.633</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>-3.674</v>
+        <v>-3.633</v>
       </c>
       <c r="I157" t="n">
         <v>-3.7255</v>
@@ -7678,7 +7678,7 @@
         <v>-2.7624</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.9181</v>
+        <v>-1.9199</v>
       </c>
       <c r="E158" t="n">
         <v>-3.7049</v>
@@ -7724,7 +7724,7 @@
         <v>-2.7768</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.9259</v>
+        <v>-1.9276</v>
       </c>
       <c r="E159" t="n">
         <v>-3.7242</v>
@@ -7764,25 +7764,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-5.0678</v>
+        <v>-4.9924</v>
       </c>
       <c r="C160" t="n">
-        <v>-3.7786</v>
+        <v>-3.7224</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.4686</v>
+        <v>-2.4329</v>
       </c>
       <c r="E160" t="n">
-        <v>-5.0678</v>
+        <v>-4.9924</v>
       </c>
       <c r="F160" t="n">
-        <v>-4.0678</v>
+        <v>-3.9924</v>
       </c>
       <c r="G160" t="n">
         <v>-1</v>
       </c>
       <c r="H160" t="n">
-        <v>-4.0678</v>
+        <v>-3.9924</v>
       </c>
       <c r="I160" t="n">
         <v>-4.1633</v>
@@ -7816,7 +7816,7 @@
         <v>-4.8335</v>
       </c>
       <c r="D161" t="n">
-        <v>-3.0402</v>
+        <v>-3.0266</v>
       </c>
       <c r="E161" t="n">
         <v>-6.4826</v>

--- a/database/event/7441/event_7441_evp_summary.xlsx
+++ b/database/event/7441/event_7441_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.978400000000001</v>
+        <v>9.296099999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>6.6944</v>
+        <v>6.9313</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4629</v>
+        <v>3.5385</v>
       </c>
       <c r="E2" t="n">
-        <v>8.978400000000001</v>
+        <v>9.296099999999999</v>
       </c>
       <c r="F2" t="n">
         <v>3.3788</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2273</v>
+        <v>8.557399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>6.1344</v>
+        <v>6.3805</v>
       </c>
       <c r="D3" t="n">
-        <v>3.121</v>
+        <v>3.2086</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2273</v>
+        <v>8.557399999999999</v>
       </c>
       <c r="F3" t="n">
         <v>4.1355</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9442</v>
+        <v>7.2244</v>
       </c>
       <c r="C4" t="n">
-        <v>5.1777</v>
+        <v>5.3866</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5369</v>
+        <v>2.6132</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9442</v>
+        <v>7.2244</v>
       </c>
       <c r="F4" t="n">
         <v>3.5871</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3148</v>
+        <v>6.8604</v>
       </c>
       <c r="C5" t="n">
-        <v>4.7084</v>
+        <v>5.1152</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2504</v>
+        <v>2.4506</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3148</v>
+        <v>6.8604</v>
       </c>
       <c r="F5" t="n">
         <v>6.5363</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.2016</v>
+        <v>6.599</v>
       </c>
       <c r="C6" t="n">
-        <v>4.624</v>
+        <v>4.9203</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1989</v>
+        <v>2.3338</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2016</v>
+        <v>6.599</v>
       </c>
       <c r="F6" t="n">
         <v>4.2168</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7428</v>
+        <v>5.8977</v>
       </c>
       <c r="C7" t="n">
-        <v>4.2819</v>
+        <v>4.3974</v>
       </c>
       <c r="D7" t="n">
-        <v>1.99</v>
+        <v>2.0206</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7428</v>
+        <v>5.8977</v>
       </c>
       <c r="F7" t="n">
         <v>3.7813</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4527</v>
+        <v>5.5618</v>
       </c>
       <c r="C8" t="n">
-        <v>4.0656</v>
+        <v>4.147</v>
       </c>
       <c r="D8" t="n">
-        <v>1.858</v>
+        <v>1.8705</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4527</v>
+        <v>5.5618</v>
       </c>
       <c r="F8" t="n">
         <v>4.0416</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3685</v>
+        <v>5.5144</v>
       </c>
       <c r="C9" t="n">
-        <v>4.0028</v>
+        <v>4.1116</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8196</v>
+        <v>1.8493</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3685</v>
+        <v>5.5144</v>
       </c>
       <c r="F9" t="n">
         <v>3.6539</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.3066</v>
+        <v>5.4448</v>
       </c>
       <c r="C10" t="n">
-        <v>3.9567</v>
+        <v>4.0597</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7915</v>
+        <v>1.8183</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3066</v>
+        <v>5.4448</v>
       </c>
       <c r="F10" t="n">
         <v>1.8642</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.1071</v>
+        <v>5.3811</v>
       </c>
       <c r="C11" t="n">
-        <v>3.8079</v>
+        <v>4.0122</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7007</v>
+        <v>1.7898</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1071</v>
+        <v>5.3811</v>
       </c>
       <c r="F11" t="n">
         <v>3.3419</v>
@@ -952,323 +952,323 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.0759</v>
+        <v>5.1477</v>
       </c>
       <c r="C12" t="n">
-        <v>3.7847</v>
+        <v>3.8382</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6865</v>
+        <v>1.6855</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0759</v>
+        <v>5.1477</v>
       </c>
       <c r="F12" t="n">
-        <v>1.316</v>
+        <v>4.7967</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7599</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.316</v>
+        <v>7.7736</v>
       </c>
       <c r="I12" t="n">
-        <v>1.316</v>
+        <v>8.179399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7599</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>148</v>
+        <v>281</v>
       </c>
       <c r="L12" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.0759</v>
+        <v>8.179399999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>361</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.0028</v>
+        <v>5.1146</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7302</v>
+        <v>3.8135</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6532</v>
+        <v>1.6708</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0028</v>
+        <v>5.1146</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3816</v>
+        <v>1.316</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6212</v>
+        <v>3.7599</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4877</v>
+        <v>1.316</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4877</v>
+        <v>1.316</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6212</v>
+        <v>3.7599</v>
       </c>
       <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
         <v>213</v>
       </c>
-      <c r="L13" t="n">
-        <v>242</v>
-      </c>
       <c r="M13" t="n">
-        <v>5.1089</v>
+        <v>5.0759</v>
       </c>
       <c r="N13" t="n">
-        <v>455</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.7967</v>
+        <v>5.0233</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5765</v>
+        <v>3.7454</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5594</v>
+        <v>1.63</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7967</v>
+        <v>5.0233</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7967</v>
+        <v>4.549</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.7736</v>
+        <v>7.2314</v>
       </c>
       <c r="I14" t="n">
-        <v>8.179399999999999</v>
+        <v>7.4177</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>8.179399999999999</v>
+        <v>7.4177</v>
       </c>
       <c r="N14" t="n">
-        <v>281</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.7195</v>
+        <v>5.0107</v>
       </c>
       <c r="C15" t="n">
-        <v>3.5189</v>
+        <v>3.736</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5242</v>
+        <v>1.6243</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7195</v>
+        <v>5.0107</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1823</v>
+        <v>2.3816</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5372</v>
+        <v>2.6212</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4289</v>
+        <v>2.4877</v>
       </c>
       <c r="I15" t="n">
-        <v>7.301</v>
+        <v>2.4877</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5372</v>
+        <v>2.6212</v>
       </c>
       <c r="K15" t="n">
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>242</v>
       </c>
       <c r="M15" t="n">
-        <v>7.838200000000001</v>
+        <v>5.1089</v>
       </c>
       <c r="N15" t="n">
-        <v>364</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.6448</v>
+        <v>4.9398</v>
       </c>
       <c r="C16" t="n">
-        <v>3.4632</v>
+        <v>3.6832</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4902</v>
+        <v>1.5927</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6448</v>
+        <v>4.9398</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4.1823</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6448</v>
+        <v>0.5372</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8412</v>
+        <v>6.4289</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8412</v>
+        <v>7.301</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6448</v>
+        <v>0.5372</v>
       </c>
       <c r="K16" t="n">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c r="L16" t="n">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>5.486000000000001</v>
+        <v>7.838200000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.549</v>
+        <v>4.7729</v>
       </c>
       <c r="C17" t="n">
-        <v>3.3918</v>
+        <v>3.5587</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4466</v>
+        <v>1.5181</v>
       </c>
       <c r="E17" t="n">
-        <v>4.549</v>
+        <v>4.7729</v>
       </c>
       <c r="F17" t="n">
-        <v>4.549</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.6448</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2314</v>
+        <v>3.8412</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4177</v>
+        <v>3.8412</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.6448</v>
       </c>
       <c r="K17" t="n">
-        <v>256</v>
+        <v>148</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="M17" t="n">
-        <v>7.4177</v>
+        <v>5.486000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>256</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.4505</v>
+        <v>4.6259</v>
       </c>
       <c r="C18" t="n">
-        <v>3.3184</v>
+        <v>3.4491</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4018</v>
+        <v>1.4525</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4505</v>
+        <v>4.6259</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4505</v>
+        <v>4.4019</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7.0157</v>
+        <v>6.9094</v>
       </c>
       <c r="I18" t="n">
-        <v>7.5722</v>
+        <v>7.8467</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7.5722</v>
+        <v>7.8467</v>
       </c>
       <c r="N18" t="n">
-        <v>359</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.4097</v>
+        <v>4.5987</v>
       </c>
       <c r="C19" t="n">
-        <v>3.2879</v>
+        <v>3.4289</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3832</v>
+        <v>1.4403</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4097</v>
+        <v>4.5987</v>
       </c>
       <c r="F19" t="n">
         <v>4.4097</v>
@@ -1320,277 +1320,277 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.4019</v>
+        <v>4.5056</v>
       </c>
       <c r="C20" t="n">
-        <v>3.2821</v>
+        <v>3.3594</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3796</v>
+        <v>1.3987</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4019</v>
+        <v>4.5056</v>
       </c>
       <c r="F20" t="n">
-        <v>4.4019</v>
+        <v>4.4505</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.9094</v>
+        <v>7.0157</v>
       </c>
       <c r="I20" t="n">
-        <v>7.8467</v>
+        <v>7.5722</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.8467</v>
+        <v>7.5722</v>
       </c>
       <c r="N20" t="n">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.1254</v>
+        <v>4.389</v>
       </c>
       <c r="C21" t="n">
-        <v>3.076</v>
+        <v>3.2725</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2538</v>
+        <v>1.3467</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1254</v>
+        <v>4.389</v>
       </c>
       <c r="F21" t="n">
-        <v>4.1254</v>
+        <v>3.7945</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6.3042</v>
+        <v>5.5801</v>
       </c>
       <c r="I21" t="n">
-        <v>6.3042</v>
+        <v>5.5801</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>6.3042</v>
+        <v>5.5801</v>
       </c>
       <c r="N21" t="n">
-        <v>312</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.0835</v>
+        <v>4.3848</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0447</v>
+        <v>3.2694</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2347</v>
+        <v>1.3448</v>
       </c>
       <c r="E22" t="n">
-        <v>4.0835</v>
+        <v>4.3848</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0835</v>
+        <v>3.9723</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2126</v>
+        <v>5.9691</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8782</v>
+        <v>5.9691</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>385</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.8782</v>
+        <v>5.9691</v>
       </c>
       <c r="N22" t="n">
-        <v>385</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.0403</v>
+        <v>4.3558</v>
       </c>
       <c r="C23" t="n">
-        <v>3.0125</v>
+        <v>3.2477</v>
       </c>
       <c r="D23" t="n">
-        <v>1.215</v>
+        <v>1.3318</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0403</v>
+        <v>4.3558</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0403</v>
+        <v>4.1254</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>6.1181</v>
+        <v>6.3042</v>
       </c>
       <c r="I23" t="n">
-        <v>6.7735</v>
+        <v>6.3042</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6.7735</v>
+        <v>6.3042</v>
       </c>
       <c r="N23" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.9723</v>
+        <v>4.2288</v>
       </c>
       <c r="C24" t="n">
-        <v>2.9618</v>
+        <v>3.153</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1841</v>
+        <v>1.2751</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9723</v>
+        <v>4.2288</v>
       </c>
       <c r="F24" t="n">
-        <v>3.9723</v>
+        <v>4.0403</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.9691</v>
+        <v>6.1181</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9691</v>
+        <v>6.7735</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>251</v>
+        <v>385</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.9691</v>
+        <v>6.7735</v>
       </c>
       <c r="N24" t="n">
-        <v>251</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.8568</v>
+        <v>4.2035</v>
       </c>
       <c r="C25" t="n">
-        <v>2.8757</v>
+        <v>3.1342</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1315</v>
+        <v>1.2638</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8568</v>
+        <v>4.2035</v>
       </c>
       <c r="F25" t="n">
-        <v>3.8568</v>
+        <v>4.0835</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>5.7164</v>
+        <v>6.2126</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4919</v>
+        <v>6.8782</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6.4919</v>
+        <v>6.8782</v>
       </c>
       <c r="N25" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="26">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.8232</v>
+        <v>4.1384</v>
       </c>
       <c r="C26" t="n">
-        <v>2.8506</v>
+        <v>3.0856</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1162</v>
+        <v>1.2347</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8232</v>
+        <v>4.1384</v>
       </c>
       <c r="F26" t="n">
         <v>4.2093</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.8147</v>
+        <v>3.9002</v>
       </c>
       <c r="C27" t="n">
-        <v>2.8443</v>
+        <v>2.908</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1123</v>
+        <v>1.1283</v>
       </c>
       <c r="E27" t="n">
-        <v>3.8147</v>
+        <v>3.9002</v>
       </c>
       <c r="F27" t="n">
-        <v>3.8147</v>
+        <v>3.8568</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6243</v>
+        <v>5.7164</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2268</v>
+        <v>6.4919</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6.2268</v>
+        <v>6.4919</v>
       </c>
       <c r="N27" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.8015</v>
+        <v>3.844</v>
       </c>
       <c r="C28" t="n">
-        <v>2.8344</v>
+        <v>2.8661</v>
       </c>
       <c r="D28" t="n">
-        <v>1.1063</v>
+        <v>1.1032</v>
       </c>
       <c r="E28" t="n">
-        <v>3.8015</v>
+        <v>3.844</v>
       </c>
       <c r="F28" t="n">
         <v>3.8015</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.7945</v>
+        <v>3.7927</v>
       </c>
       <c r="C29" t="n">
-        <v>2.8292</v>
+        <v>2.8279</v>
       </c>
       <c r="D29" t="n">
-        <v>1.1031</v>
+        <v>1.0803</v>
       </c>
       <c r="E29" t="n">
-        <v>3.7945</v>
+        <v>3.7927</v>
       </c>
       <c r="F29" t="n">
-        <v>3.7945</v>
+        <v>3.8147</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5.5801</v>
+        <v>5.6243</v>
       </c>
       <c r="I29" t="n">
-        <v>5.5801</v>
+        <v>6.2268</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>181</v>
+        <v>385</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.5801</v>
+        <v>6.2268</v>
       </c>
       <c r="N29" t="n">
-        <v>181</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.692</v>
+        <v>3.7599</v>
       </c>
       <c r="C30" t="n">
-        <v>2.7528</v>
+        <v>2.8034</v>
       </c>
       <c r="D30" t="n">
-        <v>1.0565</v>
+        <v>1.0656</v>
       </c>
       <c r="E30" t="n">
-        <v>3.692</v>
+        <v>3.7599</v>
       </c>
       <c r="F30" t="n">
         <v>3.692</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.689</v>
+        <v>3.7357</v>
       </c>
       <c r="C31" t="n">
-        <v>2.7506</v>
+        <v>2.7854</v>
       </c>
       <c r="D31" t="n">
-        <v>1.0551</v>
+        <v>1.0548</v>
       </c>
       <c r="E31" t="n">
-        <v>3.689</v>
+        <v>3.7357</v>
       </c>
       <c r="F31" t="n">
         <v>3.689</v>
@@ -1872,538 +1872,538 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.6852</v>
+        <v>3.6219</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7477</v>
+        <v>2.7005</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0534</v>
+        <v>1.004</v>
       </c>
       <c r="E32" t="n">
-        <v>3.6852</v>
+        <v>3.6219</v>
       </c>
       <c r="F32" t="n">
-        <v>2.781</v>
+        <v>3.646</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9042</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.3619</v>
+        <v>5.255</v>
       </c>
       <c r="I32" t="n">
-        <v>3.3619</v>
+        <v>5.6718</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9042</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>143</v>
+        <v>359</v>
       </c>
       <c r="L32" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2661</v>
+        <v>5.6718</v>
       </c>
       <c r="N32" t="n">
-        <v>233</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.646</v>
+        <v>3.604</v>
       </c>
       <c r="C33" t="n">
-        <v>2.7185</v>
+        <v>2.6872</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0355</v>
+        <v>0.996</v>
       </c>
       <c r="E33" t="n">
-        <v>3.646</v>
+        <v>3.604</v>
       </c>
       <c r="F33" t="n">
-        <v>3.646</v>
+        <v>2.781</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.9042</v>
       </c>
       <c r="H33" t="n">
-        <v>5.255</v>
+        <v>3.3619</v>
       </c>
       <c r="I33" t="n">
-        <v>5.6718</v>
+        <v>3.3619</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.9042</v>
       </c>
       <c r="K33" t="n">
-        <v>359</v>
+        <v>143</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M33" t="n">
-        <v>5.6718</v>
+        <v>4.2661</v>
       </c>
       <c r="N33" t="n">
-        <v>359</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.4804</v>
+        <v>3.4693</v>
       </c>
       <c r="C34" t="n">
-        <v>2.595</v>
+        <v>2.5868</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9601</v>
+        <v>0.9358</v>
       </c>
       <c r="E34" t="n">
-        <v>3.4804</v>
+        <v>3.4693</v>
       </c>
       <c r="F34" t="n">
-        <v>3.4804</v>
+        <v>3.2439</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8926</v>
+        <v>4.375</v>
       </c>
       <c r="I34" t="n">
-        <v>5.148</v>
+        <v>4.375</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5.148</v>
+        <v>4.375</v>
       </c>
       <c r="N34" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.4446</v>
+        <v>3.4678</v>
       </c>
       <c r="C35" t="n">
-        <v>2.5683</v>
+        <v>2.5856</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9438</v>
+        <v>0.9352</v>
       </c>
       <c r="E35" t="n">
-        <v>3.4446</v>
+        <v>3.4678</v>
       </c>
       <c r="F35" t="n">
-        <v>4.2211</v>
+        <v>3.4804</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7765</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>6.5138</v>
+        <v>4.8926</v>
       </c>
       <c r="I35" t="n">
-        <v>7.3974</v>
+        <v>5.148</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7765</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>6.620900000000001</v>
+        <v>5.148</v>
       </c>
       <c r="N35" t="n">
-        <v>364</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.305</v>
+        <v>3.4562</v>
       </c>
       <c r="C36" t="n">
-        <v>2.4643</v>
+        <v>2.577</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8803</v>
+        <v>0.93</v>
       </c>
       <c r="E36" t="n">
-        <v>3.305</v>
+        <v>3.4562</v>
       </c>
       <c r="F36" t="n">
-        <v>1.7048</v>
+        <v>3.2139</v>
       </c>
       <c r="G36" t="n">
-        <v>1.6002</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.7048</v>
+        <v>4.3092</v>
       </c>
       <c r="I36" t="n">
-        <v>1.7048</v>
+        <v>4.3092</v>
       </c>
       <c r="J36" t="n">
-        <v>1.6002</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L36" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.305</v>
+        <v>4.3092</v>
       </c>
       <c r="N36" t="n">
-        <v>303</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2439</v>
+        <v>3.4266</v>
       </c>
       <c r="C37" t="n">
-        <v>2.4187</v>
+        <v>2.5549</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8525</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2439</v>
+        <v>3.4266</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2439</v>
+        <v>1.7048</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.6002</v>
       </c>
       <c r="H37" t="n">
-        <v>4.375</v>
+        <v>1.7048</v>
       </c>
       <c r="I37" t="n">
-        <v>4.375</v>
+        <v>1.7048</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.6002</v>
       </c>
       <c r="K37" t="n">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M37" t="n">
-        <v>4.375</v>
+        <v>3.305</v>
       </c>
       <c r="N37" t="n">
-        <v>235</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Annihilation</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.2311</v>
+        <v>3.4117</v>
       </c>
       <c r="C38" t="n">
-        <v>2.4092</v>
+        <v>2.5438</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8467</v>
+        <v>0.9101</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2311</v>
+        <v>3.4117</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9193</v>
+        <v>3.0274</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3118</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.6645</v>
+        <v>3.9012</v>
       </c>
       <c r="I38" t="n">
-        <v>3.7589</v>
+        <v>3.9012</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3118</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.0707</v>
+        <v>3.9012</v>
       </c>
       <c r="N38" t="n">
-        <v>231</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.2139</v>
+        <v>3.4034</v>
       </c>
       <c r="C39" t="n">
-        <v>2.3963</v>
+        <v>2.5376</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8388</v>
+        <v>0.9064</v>
       </c>
       <c r="E39" t="n">
-        <v>3.2139</v>
+        <v>3.4034</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2139</v>
+        <v>4.2211</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.7765</v>
       </c>
       <c r="H39" t="n">
-        <v>4.3092</v>
+        <v>6.5138</v>
       </c>
       <c r="I39" t="n">
-        <v>4.3092</v>
+        <v>7.3974</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.7765</v>
       </c>
       <c r="K39" t="n">
-        <v>209</v>
+        <v>324</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3092</v>
+        <v>6.620900000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>209</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.1775</v>
+        <v>3.2805</v>
       </c>
       <c r="C40" t="n">
-        <v>2.3692</v>
+        <v>2.446</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8223</v>
+        <v>0.8515</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1775</v>
+        <v>3.2805</v>
       </c>
       <c r="F40" t="n">
-        <v>3.1775</v>
+        <v>3.003</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2297</v>
+        <v>3.8477</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3387</v>
+        <v>3.8477</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.3387</v>
+        <v>3.8477</v>
       </c>
       <c r="N40" t="n">
-        <v>256</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.1706</v>
+        <v>3.2623</v>
       </c>
       <c r="C41" t="n">
-        <v>2.364</v>
+        <v>2.4324</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.8434</v>
       </c>
       <c r="E41" t="n">
-        <v>3.1706</v>
+        <v>3.2623</v>
       </c>
       <c r="F41" t="n">
-        <v>3.1706</v>
+        <v>3.1775</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2145</v>
+        <v>4.2297</v>
       </c>
       <c r="I41" t="n">
-        <v>4.7862</v>
+        <v>4.3387</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>405</v>
+        <v>256</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7862</v>
+        <v>4.3387</v>
       </c>
       <c r="N41" t="n">
-        <v>405</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.1442</v>
+        <v>3.2543</v>
       </c>
       <c r="C42" t="n">
-        <v>2.3444</v>
+        <v>2.4264</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8071</v>
+        <v>0.8398</v>
       </c>
       <c r="E42" t="n">
-        <v>3.1442</v>
+        <v>3.2543</v>
       </c>
       <c r="F42" t="n">
-        <v>3.1442</v>
+        <v>2.9193</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.3118</v>
       </c>
       <c r="H42" t="n">
-        <v>4.1568</v>
+        <v>3.6645</v>
       </c>
       <c r="I42" t="n">
-        <v>4.3738</v>
+        <v>3.7589</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.3118</v>
       </c>
       <c r="K42" t="n">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3738</v>
+        <v>4.0707</v>
       </c>
       <c r="N42" t="n">
-        <v>281</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.09</v>
+        <v>3.2158</v>
       </c>
       <c r="C43" t="n">
-        <v>2.3039</v>
+        <v>2.3977</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7824</v>
+        <v>0.8226</v>
       </c>
       <c r="E43" t="n">
-        <v>3.09</v>
+        <v>3.2158</v>
       </c>
       <c r="F43" t="n">
-        <v>3.09</v>
+        <v>3.1706</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4.0382</v>
+        <v>4.2145</v>
       </c>
       <c r="I43" t="n">
-        <v>4.586</v>
+        <v>4.7862</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.586</v>
+        <v>4.7862</v>
       </c>
       <c r="N43" t="n">
         <v>405</v>
@@ -2424,369 +2424,369 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.0898</v>
+        <v>3.1917</v>
       </c>
       <c r="C44" t="n">
-        <v>2.3038</v>
+        <v>2.3798</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7823</v>
+        <v>0.8118</v>
       </c>
       <c r="E44" t="n">
-        <v>3.0898</v>
+        <v>3.1917</v>
       </c>
       <c r="F44" t="n">
-        <v>3.0898</v>
+        <v>3.09</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>4.0377</v>
+        <v>4.0382</v>
       </c>
       <c r="I44" t="n">
-        <v>4.0377</v>
+        <v>4.586</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>251</v>
+        <v>405</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.0377</v>
+        <v>4.586</v>
       </c>
       <c r="N44" t="n">
-        <v>251</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.0504</v>
+        <v>3.1476</v>
       </c>
       <c r="C45" t="n">
-        <v>2.2744</v>
+        <v>2.3469</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7644</v>
+        <v>0.7921</v>
       </c>
       <c r="E45" t="n">
-        <v>3.0504</v>
+        <v>3.1476</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0504</v>
+        <v>3.1442</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3.9515</v>
+        <v>4.1568</v>
       </c>
       <c r="I45" t="n">
-        <v>4.1578</v>
+        <v>4.3738</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1578</v>
+        <v>4.3738</v>
       </c>
       <c r="N45" t="n">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.0393</v>
+        <v>3.1008</v>
       </c>
       <c r="C46" t="n">
-        <v>2.2661</v>
+        <v>2.312</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7593</v>
+        <v>0.7712</v>
       </c>
       <c r="E46" t="n">
-        <v>3.0393</v>
+        <v>3.1008</v>
       </c>
       <c r="F46" t="n">
-        <v>1.9408</v>
+        <v>3.0898</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0985</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9408</v>
+        <v>4.0377</v>
       </c>
       <c r="I46" t="n">
-        <v>1.9408</v>
+        <v>4.0377</v>
       </c>
       <c r="J46" t="n">
-        <v>1.0985</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>147</v>
+        <v>251</v>
       </c>
       <c r="L46" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.0393</v>
+        <v>4.0377</v>
       </c>
       <c r="N46" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.0357</v>
+        <v>3.0836</v>
       </c>
       <c r="C47" t="n">
-        <v>2.2635</v>
+        <v>2.2992</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7577</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>3.0357</v>
+        <v>3.0836</v>
       </c>
       <c r="F47" t="n">
-        <v>3.0826</v>
+        <v>2.7353</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0469</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>4.0219</v>
+        <v>3.2617</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1255</v>
+        <v>3.2617</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.0469</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.0786</v>
+        <v>3.2617</v>
       </c>
       <c r="N47" t="n">
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Annihilation</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.0274</v>
+        <v>3.0656</v>
       </c>
       <c r="C48" t="n">
-        <v>2.2573</v>
+        <v>2.2858</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7539</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>3.0274</v>
+        <v>3.0656</v>
       </c>
       <c r="F48" t="n">
-        <v>3.0274</v>
+        <v>3.4607</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.486</v>
       </c>
       <c r="H48" t="n">
-        <v>3.9012</v>
+        <v>4.8495</v>
       </c>
       <c r="I48" t="n">
-        <v>3.9012</v>
+        <v>4.8495</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.486</v>
       </c>
       <c r="K48" t="n">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>3.9012</v>
+        <v>4.3635</v>
       </c>
       <c r="N48" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3.003</v>
+        <v>3.0595</v>
       </c>
       <c r="C49" t="n">
-        <v>2.2391</v>
+        <v>2.2812</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7428</v>
+        <v>0.7528</v>
       </c>
       <c r="E49" t="n">
-        <v>3.003</v>
+        <v>3.0595</v>
       </c>
       <c r="F49" t="n">
-        <v>3.003</v>
+        <v>2.8606</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3.8477</v>
+        <v>3.536</v>
       </c>
       <c r="I49" t="n">
-        <v>3.8477</v>
+        <v>3.536</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8477</v>
+        <v>3.536</v>
       </c>
       <c r="N49" t="n">
-        <v>175</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.9878</v>
+        <v>3.0462</v>
       </c>
       <c r="C50" t="n">
-        <v>2.2277</v>
+        <v>2.2713</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7359</v>
+        <v>0.7469</v>
       </c>
       <c r="E50" t="n">
-        <v>2.9878</v>
+        <v>3.0462</v>
       </c>
       <c r="F50" t="n">
-        <v>3.4738</v>
+        <v>1.9408</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.486</v>
+        <v>1.0985</v>
       </c>
       <c r="H50" t="n">
-        <v>4.8781</v>
+        <v>1.9408</v>
       </c>
       <c r="I50" t="n">
-        <v>4.8781</v>
+        <v>1.9408</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.486</v>
+        <v>1.0985</v>
       </c>
       <c r="K50" t="n">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="M50" t="n">
-        <v>4.3921</v>
+        <v>3.0393</v>
       </c>
       <c r="N50" t="n">
-        <v>230</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.9662</v>
+        <v>3.0053</v>
       </c>
       <c r="C51" t="n">
-        <v>2.2116</v>
+        <v>2.2408</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7261</v>
+        <v>0.7286</v>
       </c>
       <c r="E51" t="n">
-        <v>2.9662</v>
+        <v>3.0053</v>
       </c>
       <c r="F51" t="n">
-        <v>2.9662</v>
+        <v>3.0826</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.0469</v>
       </c>
       <c r="H51" t="n">
-        <v>3.7671</v>
+        <v>4.0219</v>
       </c>
       <c r="I51" t="n">
-        <v>3.7671</v>
+        <v>4.1255</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.0469</v>
       </c>
       <c r="K51" t="n">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7671</v>
+        <v>4.0786</v>
       </c>
       <c r="N51" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52">
@@ -2796,16 +2796,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.9625</v>
+        <v>2.9993</v>
       </c>
       <c r="C52" t="n">
-        <v>2.2089</v>
+        <v>2.2363</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7244</v>
+        <v>0.7259</v>
       </c>
       <c r="E52" t="n">
-        <v>2.9625</v>
+        <v>2.9993</v>
       </c>
       <c r="F52" t="n">
         <v>2.9625</v>
@@ -2838,231 +2838,231 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.8606</v>
+        <v>2.9633</v>
       </c>
       <c r="C53" t="n">
-        <v>2.1329</v>
+        <v>2.2095</v>
       </c>
       <c r="D53" t="n">
-        <v>0.678</v>
+        <v>0.7098</v>
       </c>
       <c r="E53" t="n">
-        <v>2.8606</v>
+        <v>2.9633</v>
       </c>
       <c r="F53" t="n">
-        <v>2.8606</v>
+        <v>3.0504</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>3.536</v>
+        <v>3.9515</v>
       </c>
       <c r="I53" t="n">
-        <v>3.536</v>
+        <v>4.1578</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.536</v>
+        <v>4.1578</v>
       </c>
       <c r="N53" t="n">
-        <v>209</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.8064</v>
+        <v>2.9455</v>
       </c>
       <c r="C54" t="n">
-        <v>2.0925</v>
+        <v>2.1962</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6533</v>
+        <v>0.7019</v>
       </c>
       <c r="E54" t="n">
-        <v>2.8064</v>
+        <v>2.9455</v>
       </c>
       <c r="F54" t="n">
-        <v>2.8064</v>
+        <v>2.9662</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3.4173</v>
+        <v>3.7671</v>
       </c>
       <c r="I54" t="n">
-        <v>3.8809</v>
+        <v>3.7671</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>374</v>
+        <v>235</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.8809</v>
+        <v>3.7671</v>
       </c>
       <c r="N54" t="n">
-        <v>374</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.7353</v>
+        <v>2.8282</v>
       </c>
       <c r="C55" t="n">
-        <v>2.0395</v>
+        <v>2.1087</v>
       </c>
       <c r="D55" t="n">
-        <v>0.621</v>
+        <v>0.6495</v>
       </c>
       <c r="E55" t="n">
-        <v>2.7353</v>
+        <v>2.8282</v>
       </c>
       <c r="F55" t="n">
-        <v>2.7353</v>
+        <v>2.6246</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3.2617</v>
+        <v>3.0195</v>
       </c>
       <c r="I55" t="n">
-        <v>3.2617</v>
+        <v>3.0195</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2617</v>
+        <v>3.0195</v>
       </c>
       <c r="N55" t="n">
-        <v>190</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.6987</v>
+        <v>2.8104</v>
       </c>
       <c r="C56" t="n">
-        <v>2.0122</v>
+        <v>2.0955</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6415</v>
       </c>
       <c r="E56" t="n">
-        <v>2.6987</v>
+        <v>2.8104</v>
       </c>
       <c r="F56" t="n">
-        <v>2.6987</v>
+        <v>2.6251</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3.1816</v>
+        <v>3.0205</v>
       </c>
       <c r="I56" t="n">
-        <v>3.1816</v>
+        <v>3.1782</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1816</v>
+        <v>3.1782</v>
       </c>
       <c r="N56" t="n">
-        <v>231</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.665</v>
+        <v>2.7655</v>
       </c>
       <c r="C57" t="n">
-        <v>1.9871</v>
+        <v>2.062</v>
       </c>
       <c r="D57" t="n">
-        <v>0.589</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>2.665</v>
+        <v>2.7655</v>
       </c>
       <c r="F57" t="n">
-        <v>2.665</v>
+        <v>2.8064</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3.108</v>
+        <v>3.4173</v>
       </c>
       <c r="I57" t="n">
-        <v>3.108</v>
+        <v>3.8809</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.108</v>
+        <v>3.8809</v>
       </c>
       <c r="N57" t="n">
-        <v>265</v>
+        <v>374</v>
       </c>
     </row>
     <row r="58">
@@ -3072,16 +3072,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.6295</v>
+        <v>2.7626</v>
       </c>
       <c r="C58" t="n">
-        <v>1.9606</v>
+        <v>2.0598</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5728</v>
+        <v>0.6202</v>
       </c>
       <c r="E58" t="n">
-        <v>2.6295</v>
+        <v>2.7626</v>
       </c>
       <c r="F58" t="n">
         <v>2.6295</v>
@@ -3114,446 +3114,446 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.6251</v>
+        <v>2.6866</v>
       </c>
       <c r="C59" t="n">
-        <v>1.9573</v>
+        <v>2.0032</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5708</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>2.6251</v>
+        <v>2.6866</v>
       </c>
       <c r="F59" t="n">
-        <v>2.6251</v>
+        <v>2.665</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3.0205</v>
+        <v>3.108</v>
       </c>
       <c r="I59" t="n">
-        <v>3.1782</v>
+        <v>3.108</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1782</v>
+        <v>3.108</v>
       </c>
       <c r="N59" t="n">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.6246</v>
+        <v>2.648</v>
       </c>
       <c r="C60" t="n">
-        <v>1.9569</v>
+        <v>1.9744</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5706</v>
+        <v>0.569</v>
       </c>
       <c r="E60" t="n">
-        <v>2.6246</v>
+        <v>2.648</v>
       </c>
       <c r="F60" t="n">
-        <v>2.6246</v>
+        <v>2.5935</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>3.0195</v>
+        <v>2.9513</v>
       </c>
       <c r="I60" t="n">
-        <v>3.0195</v>
+        <v>3.3517</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.0195</v>
+        <v>3.3517</v>
       </c>
       <c r="N60" t="n">
-        <v>235</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.5935</v>
+        <v>2.6357</v>
       </c>
       <c r="C61" t="n">
-        <v>1.9337</v>
+        <v>1.9652</v>
       </c>
       <c r="D61" t="n">
-        <v>0.5564</v>
+        <v>0.5635</v>
       </c>
       <c r="E61" t="n">
-        <v>2.5935</v>
+        <v>2.6357</v>
       </c>
       <c r="F61" t="n">
-        <v>2.5935</v>
+        <v>2.6987</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.9513</v>
+        <v>3.1816</v>
       </c>
       <c r="I61" t="n">
-        <v>3.3517</v>
+        <v>3.1816</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>405</v>
+        <v>231</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3517</v>
+        <v>3.1816</v>
       </c>
       <c r="N61" t="n">
-        <v>405</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.5841</v>
+        <v>2.6153</v>
       </c>
       <c r="C62" t="n">
-        <v>1.9267</v>
+        <v>1.95</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5521</v>
+        <v>0.5544</v>
       </c>
       <c r="E62" t="n">
-        <v>2.5841</v>
+        <v>2.6153</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5841</v>
+        <v>1.6383</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.8336</v>
       </c>
       <c r="H62" t="n">
-        <v>2.9309</v>
+        <v>1.6383</v>
       </c>
       <c r="I62" t="n">
-        <v>3.1634</v>
+        <v>1.6383</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>0.8336</v>
       </c>
       <c r="K62" t="n">
-        <v>359</v>
+        <v>143</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1634</v>
+        <v>2.4719</v>
       </c>
       <c r="N62" t="n">
-        <v>359</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.5223</v>
+        <v>2.5552</v>
       </c>
       <c r="C63" t="n">
-        <v>1.8807</v>
+        <v>1.9052</v>
       </c>
       <c r="D63" t="n">
-        <v>0.524</v>
+        <v>0.5275</v>
       </c>
       <c r="E63" t="n">
-        <v>2.5223</v>
+        <v>2.5552</v>
       </c>
       <c r="F63" t="n">
-        <v>2.5223</v>
+        <v>2.5841</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2.7955</v>
+        <v>2.9309</v>
       </c>
       <c r="I63" t="n">
-        <v>3.095</v>
+        <v>3.1634</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.095</v>
+        <v>3.1634</v>
       </c>
       <c r="N63" t="n">
-        <v>385</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2.5186</v>
+        <v>2.4794</v>
       </c>
       <c r="C64" t="n">
-        <v>1.8779</v>
+        <v>1.8487</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5223</v>
+        <v>0.4937</v>
       </c>
       <c r="E64" t="n">
-        <v>2.5186</v>
+        <v>2.4794</v>
       </c>
       <c r="F64" t="n">
-        <v>3.277</v>
+        <v>2.3754</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.7584</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>4.4473</v>
+        <v>2.474</v>
       </c>
       <c r="I64" t="n">
-        <v>4.4473</v>
+        <v>2.474</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.7584</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="L64" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6889</v>
+        <v>2.474</v>
       </c>
       <c r="N64" t="n">
-        <v>455</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.4719</v>
+        <v>2.4321</v>
       </c>
       <c r="C65" t="n">
-        <v>1.8431</v>
+        <v>1.8134</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5011</v>
+        <v>0.4725</v>
       </c>
       <c r="E65" t="n">
-        <v>2.4719</v>
+        <v>2.4321</v>
       </c>
       <c r="F65" t="n">
-        <v>1.6383</v>
+        <v>2.372</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8336</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.6383</v>
+        <v>2.4666</v>
       </c>
       <c r="I65" t="n">
-        <v>1.6383</v>
+        <v>2.4666</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8336</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="L65" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.4719</v>
+        <v>2.4666</v>
       </c>
       <c r="N65" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.4201</v>
+        <v>2.4269</v>
       </c>
       <c r="C66" t="n">
-        <v>1.8045</v>
+        <v>1.8095</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4775</v>
+        <v>0.4702</v>
       </c>
       <c r="E66" t="n">
-        <v>2.4201</v>
+        <v>2.4269</v>
       </c>
       <c r="F66" t="n">
-        <v>2.4201</v>
+        <v>2.3624</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2.572</v>
+        <v>2.4456</v>
       </c>
       <c r="I66" t="n">
-        <v>2.572</v>
+        <v>2.4456</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>2.572</v>
+        <v>2.4456</v>
       </c>
       <c r="N66" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2.3772</v>
+        <v>2.4197</v>
       </c>
       <c r="C67" t="n">
-        <v>1.7725</v>
+        <v>1.8042</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4579</v>
+        <v>0.467</v>
       </c>
       <c r="E67" t="n">
-        <v>2.3772</v>
+        <v>2.4197</v>
       </c>
       <c r="F67" t="n">
-        <v>2.3772</v>
+        <v>2.4201</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.478</v>
+        <v>2.572</v>
       </c>
       <c r="I67" t="n">
-        <v>2.478</v>
+        <v>2.572</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.478</v>
+        <v>2.572</v>
       </c>
       <c r="N67" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.3754</v>
+        <v>2.4035</v>
       </c>
       <c r="C68" t="n">
-        <v>1.7711</v>
+        <v>1.7921</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4571</v>
+        <v>0.4598</v>
       </c>
       <c r="E68" t="n">
-        <v>2.3754</v>
+        <v>2.4035</v>
       </c>
       <c r="F68" t="n">
-        <v>2.3754</v>
+        <v>2.1019</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2.474</v>
+        <v>2.1019</v>
       </c>
       <c r="I68" t="n">
-        <v>2.474</v>
+        <v>2.1019</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.474</v>
+        <v>2.1019</v>
       </c>
       <c r="N68" t="n">
         <v>183</v>
@@ -3574,93 +3574,93 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2.372</v>
+        <v>2.4005</v>
       </c>
       <c r="C69" t="n">
-        <v>1.7686</v>
+        <v>1.7898</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4556</v>
+        <v>0.4584</v>
       </c>
       <c r="E69" t="n">
-        <v>2.372</v>
+        <v>2.4005</v>
       </c>
       <c r="F69" t="n">
-        <v>2.372</v>
+        <v>3.277</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.7584</v>
       </c>
       <c r="H69" t="n">
-        <v>2.4666</v>
+        <v>4.4473</v>
       </c>
       <c r="I69" t="n">
-        <v>2.4666</v>
+        <v>4.4473</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.7584</v>
       </c>
       <c r="K69" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="M69" t="n">
-        <v>2.4666</v>
+        <v>3.6889</v>
       </c>
       <c r="N69" t="n">
-        <v>231</v>
+        <v>455</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.3624</v>
+        <v>2.3967</v>
       </c>
       <c r="C70" t="n">
-        <v>1.7614</v>
+        <v>1.787</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4512</v>
+        <v>0.4567</v>
       </c>
       <c r="E70" t="n">
-        <v>2.3624</v>
+        <v>2.3967</v>
       </c>
       <c r="F70" t="n">
-        <v>2.3624</v>
+        <v>2.5223</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.4456</v>
+        <v>2.7955</v>
       </c>
       <c r="I70" t="n">
-        <v>2.4456</v>
+        <v>3.095</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>234</v>
+        <v>385</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.4456</v>
+        <v>3.095</v>
       </c>
       <c r="N70" t="n">
-        <v>234</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71">
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.3184</v>
+        <v>2.3285</v>
       </c>
       <c r="C71" t="n">
-        <v>1.7286</v>
+        <v>1.7362</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4312</v>
+        <v>0.4263</v>
       </c>
       <c r="E71" t="n">
-        <v>2.3184</v>
+        <v>2.3285</v>
       </c>
       <c r="F71" t="n">
         <v>2.3184</v>
@@ -3712,231 +3712,231 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.2831</v>
+        <v>2.314</v>
       </c>
       <c r="C72" t="n">
-        <v>1.7023</v>
+        <v>1.7253</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4151</v>
+        <v>0.4198</v>
       </c>
       <c r="E72" t="n">
-        <v>2.2831</v>
+        <v>2.314</v>
       </c>
       <c r="F72" t="n">
-        <v>2.2831</v>
+        <v>2.3772</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.2831</v>
+        <v>2.478</v>
       </c>
       <c r="I72" t="n">
-        <v>2.2831</v>
+        <v>2.478</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.2831</v>
+        <v>2.478</v>
       </c>
       <c r="N72" t="n">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.2655</v>
+        <v>2.2637</v>
       </c>
       <c r="C73" t="n">
-        <v>1.6892</v>
+        <v>1.6878</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4071</v>
+        <v>0.3973</v>
       </c>
       <c r="E73" t="n">
-        <v>2.2655</v>
+        <v>2.2637</v>
       </c>
       <c r="F73" t="n">
-        <v>2.2655</v>
+        <v>2.2831</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2.2655</v>
+        <v>2.2831</v>
       </c>
       <c r="I73" t="n">
-        <v>2.2655</v>
+        <v>2.2831</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.2655</v>
+        <v>2.2831</v>
       </c>
       <c r="N73" t="n">
-        <v>183</v>
+        <v>265</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.2287</v>
+        <v>2.2418</v>
       </c>
       <c r="C74" t="n">
-        <v>1.6617</v>
+        <v>1.6715</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3903</v>
+        <v>0.3875</v>
       </c>
       <c r="E74" t="n">
-        <v>2.2287</v>
+        <v>2.2418</v>
       </c>
       <c r="F74" t="n">
-        <v>2.2287</v>
+        <v>2.2655</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>2.2287</v>
+        <v>2.2655</v>
       </c>
       <c r="I74" t="n">
-        <v>2.2287</v>
+        <v>2.2655</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.2287</v>
+        <v>2.2655</v>
       </c>
       <c r="N74" t="n">
-        <v>213</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.1551</v>
+        <v>2.2356</v>
       </c>
       <c r="C75" t="n">
-        <v>1.6069</v>
+        <v>1.6669</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3568</v>
+        <v>0.3848</v>
       </c>
       <c r="E75" t="n">
-        <v>2.1551</v>
+        <v>2.2356</v>
       </c>
       <c r="F75" t="n">
-        <v>2.1551</v>
+        <v>2.2287</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2.1551</v>
+        <v>2.2287</v>
       </c>
       <c r="I75" t="n">
-        <v>2.1551</v>
+        <v>2.2287</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.1551</v>
+        <v>2.2287</v>
       </c>
       <c r="N75" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.1019</v>
+        <v>2.2125</v>
       </c>
       <c r="C76" t="n">
-        <v>1.5672</v>
+        <v>1.6497</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3326</v>
+        <v>0.3745</v>
       </c>
       <c r="E76" t="n">
-        <v>2.1019</v>
+        <v>2.2125</v>
       </c>
       <c r="F76" t="n">
-        <v>2.1019</v>
+        <v>2.0383</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2.1019</v>
+        <v>2.0383</v>
       </c>
       <c r="I76" t="n">
-        <v>2.1019</v>
+        <v>2.0383</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2.1019</v>
+        <v>2.0383</v>
       </c>
       <c r="N76" t="n">
-        <v>183</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2.0576</v>
+        <v>2.1358</v>
       </c>
       <c r="C77" t="n">
-        <v>1.5342</v>
+        <v>1.5925</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3125</v>
+        <v>0.3402</v>
       </c>
       <c r="E77" t="n">
-        <v>2.0576</v>
+        <v>2.1358</v>
       </c>
       <c r="F77" t="n">
         <v>2.0576</v>
@@ -3988,185 +3988,185 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.0407</v>
+        <v>2.0415</v>
       </c>
       <c r="C78" t="n">
-        <v>1.5216</v>
+        <v>1.5222</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3048</v>
+        <v>0.2981</v>
       </c>
       <c r="E78" t="n">
-        <v>2.0407</v>
+        <v>2.0415</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0407</v>
+        <v>2.3643</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-0.4036</v>
       </c>
       <c r="H78" t="n">
-        <v>2.0407</v>
+        <v>2.4498</v>
       </c>
       <c r="I78" t="n">
-        <v>2.2593</v>
+        <v>2.4498</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>-0.4036</v>
       </c>
       <c r="K78" t="n">
-        <v>385</v>
+        <v>186</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M78" t="n">
-        <v>2.2593</v>
+        <v>2.0462</v>
       </c>
       <c r="N78" t="n">
-        <v>385</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2.0383</v>
+        <v>2.0311</v>
       </c>
       <c r="C79" t="n">
-        <v>1.5198</v>
+        <v>1.5144</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3037</v>
+        <v>0.2934</v>
       </c>
       <c r="E79" t="n">
-        <v>2.0383</v>
+        <v>2.0311</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0383</v>
+        <v>2.0407</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2.0383</v>
+        <v>2.0407</v>
       </c>
       <c r="I79" t="n">
-        <v>2.0383</v>
+        <v>2.2593</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>235</v>
+        <v>385</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>2.0383</v>
+        <v>2.2593</v>
       </c>
       <c r="N79" t="n">
-        <v>235</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.965</v>
+        <v>2.0021</v>
       </c>
       <c r="C80" t="n">
-        <v>1.4651</v>
+        <v>1.4928</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2703</v>
+        <v>0.2805</v>
       </c>
       <c r="E80" t="n">
-        <v>1.965</v>
+        <v>2.0021</v>
       </c>
       <c r="F80" t="n">
-        <v>1.965</v>
+        <v>2.1551</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1.965</v>
+        <v>2.1551</v>
       </c>
       <c r="I80" t="n">
-        <v>1.965</v>
+        <v>2.1551</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>1.965</v>
+        <v>2.1551</v>
       </c>
       <c r="N80" t="n">
-        <v>265</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.9411</v>
+        <v>1.9999</v>
       </c>
       <c r="C81" t="n">
-        <v>1.4473</v>
+        <v>1.4912</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2594</v>
+        <v>0.2795</v>
       </c>
       <c r="E81" t="n">
-        <v>1.9411</v>
+        <v>1.9999</v>
       </c>
       <c r="F81" t="n">
-        <v>2.3447</v>
+        <v>1.965</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.4036</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2.4068</v>
+        <v>1.965</v>
       </c>
       <c r="I81" t="n">
-        <v>2.4068</v>
+        <v>1.965</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.4036</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="L81" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.0032</v>
+        <v>1.965</v>
       </c>
       <c r="N81" t="n">
-        <v>230</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
@@ -4176,16 +4176,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.9149</v>
+        <v>1.9602</v>
       </c>
       <c r="C82" t="n">
-        <v>1.4278</v>
+        <v>1.4616</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2475</v>
+        <v>0.2618</v>
       </c>
       <c r="E82" t="n">
-        <v>1.9149</v>
+        <v>1.9602</v>
       </c>
       <c r="F82" t="n">
         <v>1.9149</v>
@@ -4218,415 +4218,415 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.8888</v>
+        <v>1.9068</v>
       </c>
       <c r="C83" t="n">
-        <v>1.4083</v>
+        <v>1.4217</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2356</v>
+        <v>0.2379</v>
       </c>
       <c r="E83" t="n">
-        <v>1.8888</v>
+        <v>1.9068</v>
       </c>
       <c r="F83" t="n">
-        <v>1.8888</v>
+        <v>1.8269</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1.8888</v>
+        <v>1.8269</v>
       </c>
       <c r="I83" t="n">
-        <v>2.145</v>
+        <v>1.8269</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>374</v>
+        <v>213</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.145</v>
+        <v>1.8269</v>
       </c>
       <c r="N83" t="n">
-        <v>374</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>MiQ</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.8562</v>
+        <v>1.8909</v>
       </c>
       <c r="C84" t="n">
-        <v>1.384</v>
+        <v>1.4099</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2208</v>
+        <v>0.2308</v>
       </c>
       <c r="E84" t="n">
-        <v>1.8562</v>
+        <v>1.8909</v>
       </c>
       <c r="F84" t="n">
-        <v>1.7779</v>
+        <v>1.7964</v>
       </c>
       <c r="G84" t="n">
-        <v>0.07829999999999999</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1.7779</v>
+        <v>1.7964</v>
       </c>
       <c r="I84" t="n">
-        <v>1.7779</v>
+        <v>1.7964</v>
       </c>
       <c r="J84" t="n">
-        <v>0.07829999999999999</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="L84" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1.8562</v>
+        <v>1.7964</v>
       </c>
       <c r="N84" t="n">
-        <v>230</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.8269</v>
+        <v>1.8101</v>
       </c>
       <c r="C85" t="n">
-        <v>1.3622</v>
+        <v>1.3496</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2074</v>
+        <v>0.1947</v>
       </c>
       <c r="E85" t="n">
-        <v>1.8269</v>
+        <v>1.8101</v>
       </c>
       <c r="F85" t="n">
-        <v>1.8269</v>
+        <v>1.739</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.8269</v>
+        <v>1.739</v>
       </c>
       <c r="I85" t="n">
-        <v>1.8269</v>
+        <v>1.739</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1.8269</v>
+        <v>1.739</v>
       </c>
       <c r="N85" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MiQ</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.7964</v>
+        <v>1.7562</v>
       </c>
       <c r="C86" t="n">
-        <v>1.3394</v>
+        <v>1.3094</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1936</v>
+        <v>0.1706</v>
       </c>
       <c r="E86" t="n">
-        <v>1.7964</v>
+        <v>1.7562</v>
       </c>
       <c r="F86" t="n">
-        <v>1.7964</v>
+        <v>1.8888</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.7964</v>
+        <v>1.8888</v>
       </c>
       <c r="I86" t="n">
-        <v>1.7964</v>
+        <v>2.145</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>154</v>
+        <v>374</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1.7964</v>
+        <v>2.145</v>
       </c>
       <c r="N86" t="n">
-        <v>154</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.739</v>
+        <v>1.7177</v>
       </c>
       <c r="C87" t="n">
-        <v>1.2966</v>
+        <v>1.2807</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1674</v>
+        <v>0.1534</v>
       </c>
       <c r="E87" t="n">
-        <v>1.739</v>
+        <v>1.7177</v>
       </c>
       <c r="F87" t="n">
-        <v>1.739</v>
+        <v>1.8243</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>1.739</v>
+        <v>1.8243</v>
       </c>
       <c r="I87" t="n">
-        <v>1.739</v>
+        <v>1.8243</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M87" t="n">
-        <v>1.739</v>
+        <v>1.9026</v>
       </c>
       <c r="N87" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.6851</v>
+        <v>1.6814</v>
       </c>
       <c r="C88" t="n">
-        <v>1.2564</v>
+        <v>1.2537</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1429</v>
+        <v>0.1372</v>
       </c>
       <c r="E88" t="n">
-        <v>1.6851</v>
+        <v>1.6814</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3438</v>
+        <v>1.5879</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3413</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1.3438</v>
+        <v>1.5879</v>
       </c>
       <c r="I88" t="n">
-        <v>1.3438</v>
+        <v>1.5879</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3413</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="L88" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1.6851</v>
+        <v>1.5879</v>
       </c>
       <c r="N88" t="n">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1.6521</v>
+        <v>1.6403</v>
       </c>
       <c r="C89" t="n">
-        <v>1.2318</v>
+        <v>1.223</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1279</v>
+        <v>0.1189</v>
       </c>
       <c r="E89" t="n">
-        <v>1.6521</v>
+        <v>1.6403</v>
       </c>
       <c r="F89" t="n">
-        <v>2.6521</v>
+        <v>1.6472</v>
       </c>
       <c r="G89" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>3.0796</v>
+        <v>1.6472</v>
       </c>
       <c r="I89" t="n">
-        <v>3.0796</v>
+        <v>1.6472</v>
       </c>
       <c r="J89" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="L89" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.0796</v>
+        <v>1.6472</v>
       </c>
       <c r="N89" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.6472</v>
+        <v>1.584</v>
       </c>
       <c r="C90" t="n">
-        <v>1.2282</v>
+        <v>1.1811</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1256</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>1.6472</v>
+        <v>1.584</v>
       </c>
       <c r="F90" t="n">
-        <v>1.6472</v>
+        <v>1.3438</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.3413</v>
       </c>
       <c r="H90" t="n">
-        <v>1.6472</v>
+        <v>1.3438</v>
       </c>
       <c r="I90" t="n">
-        <v>1.6472</v>
+        <v>1.3438</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>0.3413</v>
       </c>
       <c r="K90" t="n">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M90" t="n">
-        <v>1.6472</v>
+        <v>1.6851</v>
       </c>
       <c r="N90" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.5879</v>
+        <v>1.5309</v>
       </c>
       <c r="C91" t="n">
-        <v>1.184</v>
+        <v>1.1415</v>
       </c>
       <c r="D91" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>1.5879</v>
+        <v>1.5309</v>
       </c>
       <c r="F91" t="n">
-        <v>1.5879</v>
+        <v>2.6521</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H91" t="n">
-        <v>1.5879</v>
+        <v>3.0796</v>
       </c>
       <c r="I91" t="n">
-        <v>1.5879</v>
+        <v>3.0796</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K91" t="n">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M91" t="n">
-        <v>1.5879</v>
+        <v>2.0796</v>
       </c>
       <c r="N91" t="n">
-        <v>213</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92">
@@ -4636,16 +4636,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.4308</v>
+        <v>1.4958</v>
       </c>
       <c r="C92" t="n">
-        <v>1.0668</v>
+        <v>1.1153</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0271</v>
+        <v>0.0543</v>
       </c>
       <c r="E92" t="n">
-        <v>1.4308</v>
+        <v>1.4958</v>
       </c>
       <c r="F92" t="n">
         <v>1.4308</v>
@@ -4678,139 +4678,139 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>asap</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.179</v>
+        <v>1.3923</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8791</v>
+        <v>1.0381</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="E93" t="n">
-        <v>1.179</v>
+        <v>1.3923</v>
       </c>
       <c r="F93" t="n">
-        <v>1.179</v>
+        <v>1.0716</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>1.179</v>
+        <v>1.0716</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3389</v>
+        <v>1.0716</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>374</v>
+        <v>143</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1.3389</v>
+        <v>1.0716</v>
       </c>
       <c r="N93" t="n">
-        <v>374</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.1537</v>
+        <v>1.207</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8602</v>
+        <v>0.9</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.099</v>
+        <v>-0.0747</v>
       </c>
       <c r="E94" t="n">
-        <v>1.1537</v>
+        <v>1.207</v>
       </c>
       <c r="F94" t="n">
-        <v>1.2826</v>
+        <v>1.3602</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.1289</v>
+        <v>-0.2148</v>
       </c>
       <c r="H94" t="n">
-        <v>1.2826</v>
+        <v>1.3602</v>
       </c>
       <c r="I94" t="n">
-        <v>1.4566</v>
+        <v>1.3953</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.1289</v>
+        <v>-0.2148</v>
       </c>
       <c r="K94" t="n">
-        <v>324</v>
+        <v>181</v>
       </c>
       <c r="L94" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M94" t="n">
-        <v>1.3277</v>
+        <v>1.1805</v>
       </c>
       <c r="N94" t="n">
-        <v>364</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.1454</v>
+        <v>1.1801</v>
       </c>
       <c r="C95" t="n">
-        <v>0.854</v>
+        <v>0.8799</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.1028</v>
+        <v>-0.0867</v>
       </c>
       <c r="E95" t="n">
-        <v>1.1454</v>
+        <v>1.1801</v>
       </c>
       <c r="F95" t="n">
-        <v>1.3602</v>
+        <v>1.179</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.2148</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1.3602</v>
+        <v>1.179</v>
       </c>
       <c r="I95" t="n">
-        <v>1.3953</v>
+        <v>1.3389</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.2148</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>181</v>
+        <v>374</v>
       </c>
       <c r="L95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1.1805</v>
+        <v>1.3389</v>
       </c>
       <c r="N95" t="n">
-        <v>231</v>
+        <v>374</v>
       </c>
     </row>
     <row r="96">
@@ -4820,16 +4820,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1.1414</v>
+        <v>1.0891</v>
       </c>
       <c r="C96" t="n">
-        <v>0.851</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1046</v>
+        <v>-0.1273</v>
       </c>
       <c r="E96" t="n">
-        <v>1.1414</v>
+        <v>1.0891</v>
       </c>
       <c r="F96" t="n">
         <v>1.4353</v>
@@ -4862,875 +4862,875 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>asap</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.0716</v>
+        <v>0.9795</v>
       </c>
       <c r="C97" t="n">
-        <v>0.799</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.1364</v>
+        <v>-0.1763</v>
       </c>
       <c r="E97" t="n">
-        <v>1.0716</v>
+        <v>0.9795</v>
       </c>
       <c r="F97" t="n">
-        <v>1.0716</v>
+        <v>1.0186</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1.0716</v>
+        <v>1.0186</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0716</v>
+        <v>1.0186</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1.0716</v>
+        <v>1.0186</v>
       </c>
       <c r="N97" t="n">
-        <v>143</v>
+        <v>235</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>try</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.0186</v>
+        <v>0.9577</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7595</v>
+        <v>0.7141</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.1605</v>
+        <v>-0.186</v>
       </c>
       <c r="E98" t="n">
-        <v>1.0186</v>
+        <v>0.9577</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0186</v>
+        <v>0.7931</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1.0186</v>
+        <v>0.7931</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0186</v>
+        <v>0.7931</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>1.0186</v>
+        <v>0.7931</v>
       </c>
       <c r="N98" t="n">
-        <v>235</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8593</v>
+        <v>0.9208</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6407</v>
+        <v>0.6866</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.233</v>
+        <v>-0.2025</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8593</v>
+        <v>0.9208</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8593</v>
+        <v>1.2826</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>-0.1289</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8593</v>
+        <v>1.2826</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9275</v>
+        <v>1.4566</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>-0.1289</v>
       </c>
       <c r="K99" t="n">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M99" t="n">
-        <v>0.9275</v>
+        <v>1.3277</v>
       </c>
       <c r="N99" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.853</v>
+        <v>0.8238</v>
       </c>
       <c r="C100" t="n">
-        <v>0.636</v>
+        <v>0.6142</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2359</v>
+        <v>-0.2458</v>
       </c>
       <c r="E100" t="n">
-        <v>0.853</v>
+        <v>0.8238</v>
       </c>
       <c r="F100" t="n">
-        <v>1.4904</v>
+        <v>0.8593</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.6374</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1.4904</v>
+        <v>0.8593</v>
       </c>
       <c r="I100" t="n">
-        <v>1.4904</v>
+        <v>0.9275</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.6374</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>216</v>
+        <v>359</v>
       </c>
       <c r="L100" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0.853</v>
+        <v>0.9275</v>
       </c>
       <c r="N100" t="n">
-        <v>303</v>
+        <v>359</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8358</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6232</v>
+        <v>0.525</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.2437</v>
+        <v>-0.2993</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8358</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8358</v>
+        <v>1.4904</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>-0.6374</v>
       </c>
       <c r="H101" t="n">
-        <v>0.8358</v>
+        <v>1.4904</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8358</v>
+        <v>1.4904</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>-0.6374</v>
       </c>
       <c r="K101" t="n">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8358</v>
+        <v>0.853</v>
       </c>
       <c r="N101" t="n">
-        <v>234</v>
+        <v>303</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>try</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8163</v>
+        <v>0.6946</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6086</v>
+        <v>0.5179</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.2526</v>
+        <v>-0.3036</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8163</v>
+        <v>0.6946</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8163</v>
+        <v>0.8358</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.8163</v>
+        <v>0.8358</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8163</v>
+        <v>0.8358</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.8163</v>
+        <v>0.8358</v>
       </c>
       <c r="N102" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6661</v>
+        <v>0.5747</v>
       </c>
       <c r="C103" t="n">
-        <v>0.4967</v>
+        <v>0.4285</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.321</v>
+        <v>-0.3571</v>
       </c>
       <c r="E103" t="n">
-        <v>0.6661</v>
+        <v>0.5747</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6661</v>
+        <v>0.3737</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.1964</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6661</v>
+        <v>0.3737</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6661</v>
+        <v>0.3737</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>0.1964</v>
       </c>
       <c r="K103" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M103" t="n">
-        <v>0.6661</v>
+        <v>0.5700999999999999</v>
       </c>
       <c r="N103" t="n">
-        <v>135</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5007</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4724</v>
+        <v>0.3733</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.3358</v>
+        <v>-0.3902</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5007</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6661</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6661</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6499</v>
+        <v>0.6661</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0.6499</v>
+        <v>0.6661</v>
       </c>
       <c r="N104" t="n">
-        <v>256</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5397</v>
+        <v>0.484</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4024</v>
+        <v>0.3609</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.3785</v>
+        <v>-0.3976</v>
       </c>
       <c r="E105" t="n">
-        <v>0.5397</v>
+        <v>0.484</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3433</v>
+        <v>0.4723</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1964</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.3433</v>
+        <v>0.4723</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3433</v>
+        <v>0.4723</v>
       </c>
       <c r="J105" t="n">
-        <v>0.1964</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L105" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0.5397</v>
+        <v>0.4723</v>
       </c>
       <c r="N105" t="n">
-        <v>230</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4723</v>
+        <v>0.4526</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3522</v>
+        <v>0.3375</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.4092</v>
+        <v>-0.4117</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4723</v>
+        <v>0.4526</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4723</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.4723</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4723</v>
+        <v>0.6499</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>175</v>
+        <v>256</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0.4723</v>
+        <v>0.6499</v>
       </c>
       <c r="N106" t="n">
-        <v>175</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.3103</v>
+        <v>0.4194</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2314</v>
+        <v>0.3127</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.4829</v>
+        <v>-0.4265</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3103</v>
+        <v>0.4194</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3103</v>
+        <v>0.2971</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.3103</v>
+        <v>0.2971</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3103</v>
+        <v>0.2971</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>0.3103</v>
+        <v>0.2971</v>
       </c>
       <c r="N107" t="n">
-        <v>209</v>
+        <v>135</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kabal</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.3093</v>
+        <v>0.3916</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2306</v>
+        <v>0.292</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.4834</v>
+        <v>-0.4389</v>
       </c>
       <c r="E108" t="n">
-        <v>0.3093</v>
+        <v>0.3916</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3093</v>
+        <v>0.1257</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3093</v>
+        <v>0.1257</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3093</v>
+        <v>0.1257</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0.3093</v>
+        <v>0.1257</v>
       </c>
       <c r="N108" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.2971</v>
+        <v>0.3859</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2215</v>
+        <v>0.2877</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.489</v>
+        <v>-0.4414</v>
       </c>
       <c r="E109" t="n">
-        <v>0.2971</v>
+        <v>0.3859</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2971</v>
+        <v>0.2557</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0.2971</v>
+        <v>0.2557</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2971</v>
+        <v>0.2557</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>0.2971</v>
+        <v>0.2557</v>
       </c>
       <c r="N109" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.2557</v>
+        <v>0.3326</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1907</v>
+        <v>0.248</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.5078</v>
+        <v>-0.4653</v>
       </c>
       <c r="E110" t="n">
-        <v>0.2557</v>
+        <v>0.3326</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2557</v>
+        <v>0.3458</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.2557</v>
+        <v>0.3458</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2557</v>
+        <v>0.3458</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>0.2557</v>
+        <v>0.3458</v>
       </c>
       <c r="N110" t="n">
-        <v>181</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.2485</v>
+        <v>0.3116</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1853</v>
+        <v>0.2323</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.5111</v>
+        <v>-0.4746</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2485</v>
+        <v>0.3116</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2485</v>
+        <v>0.2238</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2485</v>
+        <v>0.2238</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2485</v>
+        <v>0.2238</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0.2485</v>
+        <v>0.2238</v>
       </c>
       <c r="N111" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.2238</v>
+        <v>0.1801</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1669</v>
+        <v>0.1343</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.5223</v>
+        <v>-0.5334</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2238</v>
+        <v>0.1801</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2238</v>
+        <v>0.1679</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2238</v>
+        <v>0.1679</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2238</v>
+        <v>0.1679</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>190</v>
+        <v>312</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0.2238</v>
+        <v>0.1679</v>
       </c>
       <c r="N112" t="n">
-        <v>190</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1829</v>
+        <v>0.1346</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1364</v>
+        <v>0.1004</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.5409</v>
+        <v>-0.5537</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1829</v>
+        <v>0.1346</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1829</v>
+        <v>0.2485</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1829</v>
+        <v>0.2485</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1924</v>
+        <v>0.2485</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0.1924</v>
+        <v>0.2485</v>
       </c>
       <c r="N113" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>kabal</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1679</v>
+        <v>0.11</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1252</v>
+        <v>0.082</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.5478</v>
+        <v>-0.5647</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1679</v>
+        <v>0.11</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1679</v>
+        <v>0.3093</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1679</v>
+        <v>0.3093</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1679</v>
+        <v>0.3093</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>312</v>
+        <v>154</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0.1679</v>
+        <v>0.3093</v>
       </c>
       <c r="N114" t="n">
-        <v>312</v>
+        <v>154</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1257</v>
+        <v>0.0965</v>
       </c>
       <c r="C115" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5707</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1257</v>
+        <v>0.0965</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1257</v>
+        <v>0.1829</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1257</v>
+        <v>0.1829</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1257</v>
+        <v>0.1924</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>0.1257</v>
+        <v>0.1924</v>
       </c>
       <c r="N115" t="n">
-        <v>135</v>
+        <v>281</v>
       </c>
     </row>
     <row r="116">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1219</v>
+        <v>-0.017</v>
       </c>
       <c r="C116" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.0127</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.5687</v>
+        <v>-0.6214</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1219</v>
+        <v>-0.017</v>
       </c>
       <c r="F116" t="n">
         <v>0.1219</v>
@@ -5782,415 +5782,415 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.0311</v>
+        <v>-0.1319</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0232</v>
+        <v>-0.0983</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6384</v>
+        <v>-0.6727</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.0311</v>
+        <v>-0.1319</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.0311</v>
+        <v>-0.0838</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.0311</v>
+        <v>-0.0838</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0311</v>
+        <v>-0.0838</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.0311</v>
+        <v>-0.0838</v>
       </c>
       <c r="N117" t="n">
-        <v>175</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.0838</v>
+        <v>-0.1945</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.0625</v>
+        <v>-0.145</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.6624</v>
+        <v>-0.7007</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.0838</v>
+        <v>-0.1945</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.0838</v>
+        <v>-0.0311</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.0838</v>
+        <v>-0.0311</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0838</v>
+        <v>-0.0311</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>312</v>
+        <v>175</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.0838</v>
+        <v>-0.0311</v>
       </c>
       <c r="N118" t="n">
-        <v>312</v>
+        <v>175</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>flying</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1983</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.11</v>
+        <v>-0.1479</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.6913</v>
+        <v>-0.7024</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1983</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1819</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1819</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1819</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.1475</v>
+        <v>-0.1819</v>
       </c>
       <c r="N119" t="n">
-        <v>181</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>chelleos</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.1669</v>
+        <v>-0.2093</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.1244</v>
+        <v>-0.1561</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.7002</v>
+        <v>-0.7073</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.1669</v>
+        <v>-0.2093</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.1669</v>
+        <v>-0.4125</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.1669</v>
+        <v>-0.4125</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1669</v>
+        <v>-0.4125</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>-0.1669</v>
+        <v>-0.4125</v>
       </c>
       <c r="N120" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>flying</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.1819</v>
+        <v>-0.2784</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.1356</v>
+        <v>-0.2076</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.707</v>
+        <v>-0.7382</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.1819</v>
+        <v>-0.2784</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.1819</v>
+        <v>-0.1475</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.1819</v>
+        <v>-0.1475</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1819</v>
+        <v>-0.1475</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.1819</v>
+        <v>-0.1475</v>
       </c>
       <c r="N121" t="n">
-        <v>235</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dobu</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2838</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.1721</v>
+        <v>-0.2116</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.7406</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2838</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2899</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2899</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2899</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.2308</v>
+        <v>-0.2899</v>
       </c>
       <c r="N122" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.258</v>
+        <v>-0.3182</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.1924</v>
+        <v>-0.2373</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.7417</v>
+        <v>-0.756</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.258</v>
+        <v>-0.3182</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0571</v>
+        <v>-0.1669</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.3151</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0571</v>
+        <v>-0.1669</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0586</v>
+        <v>-0.1669</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.3151</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L123" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.2565</v>
+        <v>-0.1669</v>
       </c>
       <c r="N123" t="n">
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-0.2899</v>
+        <v>-0.3446</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.2162</v>
+        <v>-0.2569</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.7562</v>
+        <v>-0.7677</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.2899</v>
+        <v>-0.3446</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.2899</v>
+        <v>0.0571</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>-0.3151</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.2899</v>
+        <v>0.0571</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2899</v>
+        <v>0.0586</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>-0.3151</v>
       </c>
       <c r="K124" t="n">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.2899</v>
+        <v>-0.2565</v>
       </c>
       <c r="N124" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chelleos</t>
+          <t>dobu</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.4125</v>
+        <v>-0.385</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.3076</v>
+        <v>-0.2871</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.4125</v>
+        <v>-0.385</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.4125</v>
+        <v>-0.2308</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.4125</v>
+        <v>-0.2308</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4125</v>
+        <v>-0.2308</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.4125</v>
+        <v>-0.2308</v>
       </c>
       <c r="N125" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126">
@@ -6200,16 +6200,16 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.5184</v>
+        <v>-0.6109</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.3865</v>
+        <v>-0.4555</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.8602</v>
+        <v>-0.8867</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.5184</v>
+        <v>-0.6109</v>
       </c>
       <c r="F126" t="n">
         <v>-0.5184</v>
@@ -6242,93 +6242,93 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>afufu</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.5468</v>
+        <v>-0.661</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.4077</v>
+        <v>-0.4929</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.8731</v>
+        <v>-0.9091</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.5468</v>
+        <v>-0.661</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.5468</v>
+        <v>-0.6037</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.5468</v>
+        <v>-0.6037</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.5468</v>
+        <v>-0.6037</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.5468</v>
+        <v>-0.6037</v>
       </c>
       <c r="N127" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>afufu</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.6037</v>
+        <v>-0.7024</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.4501</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.899</v>
+        <v>-0.9276</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.6037</v>
+        <v>-0.7024</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.6037</v>
+        <v>-0.5468</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.6037</v>
+        <v>-0.5468</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.6037</v>
+        <v>-0.5468</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.6037</v>
+        <v>-0.5468</v>
       </c>
       <c r="N128" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="129">
@@ -6338,16 +6338,16 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.6465</v>
+        <v>-0.8262</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.482</v>
+        <v>-0.616</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.9185</v>
+        <v>-0.9829</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.6465</v>
+        <v>-0.8262</v>
       </c>
       <c r="F129" t="n">
         <v>-0.6465</v>
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.862</v>
+        <v>-1.0582</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.6427</v>
+        <v>-0.789</v>
       </c>
       <c r="D130" t="n">
-        <v>-1.0166</v>
+        <v>-1.0865</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.862</v>
+        <v>-1.0582</v>
       </c>
       <c r="F130" t="n">
         <v>-0.862</v>
@@ -6426,139 +6426,139 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.955</v>
+        <v>-1.1281</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.7121</v>
+        <v>-0.8411</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.0589</v>
+        <v>-1.1177</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.955</v>
+        <v>-1.1281</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.955</v>
+        <v>-1.0687</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.955</v>
+        <v>-1.0687</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0846</v>
+        <v>-1.0687</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-1.0846</v>
+        <v>-1.0687</v>
       </c>
       <c r="N131" t="n">
-        <v>405</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-1.0579</v>
+        <v>-1.2668</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.9445</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.1058</v>
+        <v>-1.1797</v>
       </c>
       <c r="E132" t="n">
-        <v>-1.0579</v>
+        <v>-1.2668</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.0579</v>
+        <v>-0.955</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.0579</v>
+        <v>-0.955</v>
       </c>
       <c r="I132" t="n">
-        <v>-1.0579</v>
+        <v>-1.0846</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>175</v>
+        <v>405</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>-1.0579</v>
+        <v>-1.0846</v>
       </c>
       <c r="N132" t="n">
-        <v>175</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>dav1g</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-1.0687</v>
+        <v>-1.3057</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.7968</v>
+        <v>-0.9735</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.1107</v>
+        <v>-1.197</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.0687</v>
+        <v>-1.3057</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.0687</v>
+        <v>-1.1973</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.0687</v>
+        <v>-1.1973</v>
       </c>
       <c r="I133" t="n">
-        <v>-1.0687</v>
+        <v>-1.1973</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-1.0687</v>
+        <v>-1.1973</v>
       </c>
       <c r="N133" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134">
@@ -6568,16 +6568,16 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.1537</v>
+        <v>-1.3218</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.8602</v>
+        <v>-0.9856</v>
       </c>
       <c r="D134" t="n">
-        <v>-1.1494</v>
+        <v>-1.2042</v>
       </c>
       <c r="E134" t="n">
-        <v>-1.1537</v>
+        <v>-1.3218</v>
       </c>
       <c r="F134" t="n">
         <v>-1.1537</v>
@@ -6610,170 +6610,170 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>adamS</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-1.1584</v>
+        <v>-1.3331</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.8637</v>
+        <v>-0.994</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.1515</v>
+        <v>-1.2093</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.1584</v>
+        <v>-1.3331</v>
       </c>
       <c r="F135" t="n">
-        <v>-1.1584</v>
+        <v>-1.2478</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-1.1584</v>
+        <v>-1.2478</v>
       </c>
       <c r="I135" t="n">
-        <v>-1.1584</v>
+        <v>-1.2478</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>-1.1584</v>
+        <v>-1.2478</v>
       </c>
       <c r="N135" t="n">
-        <v>183</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>dav1g</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-1.1973</v>
+        <v>-1.3367</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.8927</v>
+        <v>-0.9967</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.1692</v>
+        <v>-1.2109</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.1973</v>
+        <v>-1.3367</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.1973</v>
+        <v>-1.0579</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.1973</v>
+        <v>-1.0579</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1973</v>
+        <v>-1.0579</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-1.1973</v>
+        <v>-1.0579</v>
       </c>
       <c r="N136" t="n">
-        <v>111</v>
+        <v>175</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>dangeR</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-1.1974</v>
+        <v>-1.3719</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.8928</v>
+        <v>-1.0229</v>
       </c>
       <c r="D137" t="n">
-        <v>-1.1693</v>
+        <v>-1.2266</v>
       </c>
       <c r="E137" t="n">
-        <v>-1.1974</v>
+        <v>-1.3719</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.1974</v>
+        <v>-1.1584</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.1974</v>
+        <v>-1.1584</v>
       </c>
       <c r="I137" t="n">
-        <v>-1.1974</v>
+        <v>-1.1584</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-1.1974</v>
+        <v>-1.1584</v>
       </c>
       <c r="N137" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>adamS</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3778</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.9304</v>
+        <v>-1.0273</v>
       </c>
       <c r="D138" t="n">
-        <v>-1.1922</v>
+        <v>-1.2293</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3778</v>
       </c>
       <c r="F138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3484</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3484</v>
       </c>
       <c r="I138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3484</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>-1.2478</v>
+        <v>-1.3484</v>
       </c>
       <c r="N138" t="n">
         <v>111</v>
@@ -6794,93 +6794,93 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>dangeR</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-1.2962</v>
+        <v>-1.3897</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.9665</v>
+        <v>-1.0362</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.2143</v>
+        <v>-1.2346</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.2962</v>
+        <v>-1.3897</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.2962</v>
+        <v>-1.1974</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.2962</v>
+        <v>-1.1974</v>
       </c>
       <c r="I139" t="n">
-        <v>-1.2962</v>
+        <v>-1.1974</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-1.2962</v>
+        <v>-1.1974</v>
       </c>
       <c r="N139" t="n">
-        <v>231</v>
+        <v>143</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-1.3484</v>
+        <v>-1.4056</v>
       </c>
       <c r="C140" t="n">
-        <v>-1.0054</v>
+        <v>-1.048</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.238</v>
+        <v>-1.2417</v>
       </c>
       <c r="E140" t="n">
-        <v>-1.3484</v>
+        <v>-1.4056</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.3484</v>
+        <v>-1.2962</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.3484</v>
+        <v>-1.2962</v>
       </c>
       <c r="I140" t="n">
-        <v>-1.3484</v>
+        <v>-1.2962</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>-1.3484</v>
+        <v>-1.2962</v>
       </c>
       <c r="N140" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
     </row>
     <row r="141">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-1.4377</v>
+        <v>-1.7456</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.072</v>
+        <v>-1.3015</v>
       </c>
       <c r="D141" t="n">
-        <v>-1.2787</v>
+        <v>-1.3935</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.4377</v>
+        <v>-1.7456</v>
       </c>
       <c r="F141" t="n">
         <v>-0.8605</v>
@@ -6932,47 +6932,47 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.5262</v>
+        <v>-1.8069</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.138</v>
+        <v>-1.3472</v>
       </c>
       <c r="D142" t="n">
-        <v>-1.319</v>
+        <v>-1.4209</v>
       </c>
       <c r="E142" t="n">
-        <v>-1.5262</v>
+        <v>-1.8069</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3472</v>
+        <v>-1.7869</v>
       </c>
       <c r="G142" t="n">
-        <v>-1.8734</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3472</v>
+        <v>-1.7869</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3472</v>
+        <v>-1.8802</v>
       </c>
       <c r="J142" t="n">
-        <v>-1.8734</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>148</v>
+        <v>289</v>
       </c>
       <c r="L142" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>-1.5262</v>
+        <v>-1.8802</v>
       </c>
       <c r="N142" t="n">
-        <v>361</v>
+        <v>289</v>
       </c>
     </row>
     <row r="143">
@@ -6982,16 +6982,16 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-1.5692</v>
+        <v>-1.8301</v>
       </c>
       <c r="C143" t="n">
-        <v>-1.17</v>
+        <v>-1.3645</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.3385</v>
+        <v>-1.4313</v>
       </c>
       <c r="E143" t="n">
-        <v>-1.5692</v>
+        <v>-1.8301</v>
       </c>
       <c r="F143" t="n">
         <v>-1.5692</v>
@@ -7028,28 +7028,28 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.667</v>
+        <v>-1.9273</v>
       </c>
       <c r="C144" t="n">
-        <v>-1.2429</v>
+        <v>-1.437</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.3831</v>
+        <v>-1.4747</v>
       </c>
       <c r="E144" t="n">
-        <v>-1.667</v>
+        <v>-1.9273</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.5928</v>
+        <v>-1.5938</v>
       </c>
       <c r="G144" t="n">
         <v>-0.0742</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.5928</v>
+        <v>-1.5938</v>
       </c>
       <c r="I144" t="n">
-        <v>-1.5928</v>
+        <v>-1.5938</v>
       </c>
       <c r="J144" t="n">
         <v>-0.0742</v>
@@ -7061,7 +7061,7 @@
         <v>44</v>
       </c>
       <c r="M144" t="n">
-        <v>-1.667</v>
+        <v>-1.668</v>
       </c>
       <c r="N144" t="n">
         <v>230</v>
@@ -7070,599 +7070,599 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-1.6769</v>
+        <v>-1.9411</v>
       </c>
       <c r="C145" t="n">
-        <v>-1.2503</v>
+        <v>-1.4473</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.3876</v>
+        <v>-1.4809</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.6769</v>
+        <v>-1.9411</v>
       </c>
       <c r="F145" t="n">
-        <v>-1.6769</v>
+        <v>-1.8955</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>-1.6769</v>
+        <v>-1.8955</v>
       </c>
       <c r="I145" t="n">
-        <v>-1.6769</v>
+        <v>-1.8955</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>-1.6769</v>
+        <v>-1.8955</v>
       </c>
       <c r="N145" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-1.6935</v>
+        <v>-1.9446</v>
       </c>
       <c r="C146" t="n">
-        <v>-1.2627</v>
+        <v>-1.4499</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.3951</v>
+        <v>-1.4824</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.6935</v>
+        <v>-1.9446</v>
       </c>
       <c r="F146" t="n">
-        <v>-1.6935</v>
+        <v>0.3472</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>-1.8734</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.6935</v>
+        <v>0.3472</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.6935</v>
+        <v>0.3472</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>-1.8734</v>
       </c>
       <c r="K146" t="n">
+        <v>148</v>
+      </c>
+      <c r="L146" t="n">
         <v>213</v>
       </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
       <c r="M146" t="n">
-        <v>-1.6935</v>
+        <v>-1.5262</v>
       </c>
       <c r="N146" t="n">
-        <v>213</v>
+        <v>361</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.6977</v>
+        <v>-1.9494</v>
       </c>
       <c r="C147" t="n">
-        <v>-1.2658</v>
+        <v>-1.4535</v>
       </c>
       <c r="D147" t="n">
-        <v>-1.397</v>
+        <v>-1.4846</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.6977</v>
+        <v>-1.9494</v>
       </c>
       <c r="F147" t="n">
-        <v>-1.6977</v>
+        <v>-1.6935</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>-1.6977</v>
+        <v>-1.6935</v>
       </c>
       <c r="I147" t="n">
-        <v>-1.6977</v>
+        <v>-1.6935</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>-1.6977</v>
+        <v>-1.6935</v>
       </c>
       <c r="N147" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-1.7869</v>
+        <v>-2.0218</v>
       </c>
       <c r="C148" t="n">
-        <v>-1.3323</v>
+        <v>-1.5075</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.4376</v>
+        <v>-1.5169</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.7869</v>
+        <v>-2.0218</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.7869</v>
+        <v>-1.6769</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.7869</v>
+        <v>-1.6769</v>
       </c>
       <c r="I148" t="n">
-        <v>-1.8802</v>
+        <v>-1.6769</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>289</v>
+        <v>181</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.8802</v>
+        <v>-1.6769</v>
       </c>
       <c r="N148" t="n">
-        <v>289</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-1.79</v>
+        <v>-2.1302</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.3346</v>
+        <v>-1.5883</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.439</v>
+        <v>-1.5653</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.79</v>
+        <v>-2.1302</v>
       </c>
       <c r="F149" t="n">
-        <v>-1.79</v>
+        <v>-1.7166</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>-1.79</v>
+        <v>-1.7166</v>
       </c>
       <c r="I149" t="n">
-        <v>-1.79</v>
+        <v>-1.7166</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>-1.79</v>
+        <v>-1.7166</v>
       </c>
       <c r="N149" t="n">
-        <v>251</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-1.8955</v>
+        <v>-2.2393</v>
       </c>
       <c r="C150" t="n">
-        <v>-1.4133</v>
+        <v>-1.6697</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.4871</v>
+        <v>-1.6141</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.8955</v>
+        <v>-2.2393</v>
       </c>
       <c r="F150" t="n">
-        <v>-1.8955</v>
+        <v>-1.79</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.8955</v>
+        <v>-1.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-1.8955</v>
+        <v>-1.79</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>-1.8955</v>
+        <v>-1.79</v>
       </c>
       <c r="N150" t="n">
-        <v>183</v>
+        <v>251</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>nython</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-2.0036</v>
+        <v>-2.281</v>
       </c>
       <c r="C151" t="n">
-        <v>-1.4939</v>
+        <v>-1.7007</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.5363</v>
+        <v>-1.6327</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.0036</v>
+        <v>-2.281</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.0036</v>
+        <v>-2.0585</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>-2.0036</v>
+        <v>-2.0585</v>
       </c>
       <c r="I151" t="n">
-        <v>-2.0036</v>
+        <v>-2.0585</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>-2.0036</v>
+        <v>-2.0585</v>
       </c>
       <c r="N151" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>nython</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-2.0585</v>
+        <v>-2.3846</v>
       </c>
       <c r="C152" t="n">
-        <v>-1.5348</v>
+        <v>-1.778</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.5613</v>
+        <v>-1.679</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.0585</v>
+        <v>-2.3846</v>
       </c>
       <c r="F152" t="n">
-        <v>-2.0585</v>
+        <v>-0.459</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>-1.6062</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.0585</v>
+        <v>-0.459</v>
       </c>
       <c r="I152" t="n">
-        <v>-2.0585</v>
+        <v>-0.459</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>-1.6062</v>
       </c>
       <c r="K152" t="n">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M152" t="n">
-        <v>-2.0585</v>
+        <v>-2.0652</v>
       </c>
       <c r="N152" t="n">
-        <v>235</v>
+        <v>303</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-2.0652</v>
+        <v>-2.438</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.5398</v>
+        <v>-1.8178</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.5643</v>
+        <v>-1.7028</v>
       </c>
       <c r="E153" t="n">
-        <v>-2.0652</v>
+        <v>-2.438</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.459</v>
+        <v>-2.3248</v>
       </c>
       <c r="G153" t="n">
-        <v>-1.6062</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.459</v>
+        <v>-2.3248</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.459</v>
+        <v>-2.3248</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.6062</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="L153" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.0652</v>
+        <v>-2.3248</v>
       </c>
       <c r="N153" t="n">
-        <v>303</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-2.1855</v>
+        <v>-2.4784</v>
       </c>
       <c r="C154" t="n">
-        <v>-1.6295</v>
+        <v>-1.8479</v>
       </c>
       <c r="D154" t="n">
-        <v>-1.6191</v>
+        <v>-1.7209</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.1855</v>
+        <v>-2.4784</v>
       </c>
       <c r="F154" t="n">
-        <v>-2.1855</v>
+        <v>-2.0036</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.1855</v>
+        <v>-2.0036</v>
       </c>
       <c r="I154" t="n">
-        <v>-2.1855</v>
+        <v>-2.0036</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>-2.1855</v>
+        <v>-2.0036</v>
       </c>
       <c r="N154" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.3248</v>
+        <v>-2.5972</v>
       </c>
       <c r="C155" t="n">
-        <v>-1.7334</v>
+        <v>-1.9365</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.6825</v>
+        <v>-1.7739</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.3248</v>
+        <v>-2.5972</v>
       </c>
       <c r="F155" t="n">
-        <v>-2.3248</v>
+        <v>-2.1855</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>-2.3248</v>
+        <v>-2.1855</v>
       </c>
       <c r="I155" t="n">
-        <v>-2.3248</v>
+        <v>-2.1855</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>-2.3248</v>
+        <v>-2.1855</v>
       </c>
       <c r="N155" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-2.6012</v>
+        <v>-2.8246</v>
       </c>
       <c r="C156" t="n">
-        <v>-1.9395</v>
+        <v>-2.1061</v>
       </c>
       <c r="D156" t="n">
-        <v>-1.8083</v>
+        <v>-1.8755</v>
       </c>
       <c r="E156" t="n">
-        <v>-2.6012</v>
+        <v>-2.8246</v>
       </c>
       <c r="F156" t="n">
-        <v>-2.6012</v>
+        <v>-2.6125</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.6012</v>
+        <v>-2.6125</v>
       </c>
       <c r="I156" t="n">
-        <v>-2.6012</v>
+        <v>-2.8197</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>-2.6012</v>
+        <v>-2.8197</v>
       </c>
       <c r="N156" t="n">
-        <v>213</v>
+        <v>359</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.6125</v>
+        <v>-2.8672</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.9479</v>
+        <v>-2.1378</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.8135</v>
+        <v>-1.8945</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.6125</v>
+        <v>-2.8672</v>
       </c>
       <c r="F157" t="n">
-        <v>-2.6125</v>
+        <v>-2.6012</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.6125</v>
+        <v>-2.6012</v>
       </c>
       <c r="I157" t="n">
-        <v>-2.8197</v>
+        <v>-2.6012</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>359</v>
+        <v>213</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>-2.8197</v>
+        <v>-2.6012</v>
       </c>
       <c r="N157" t="n">
-        <v>359</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158">
@@ -7672,16 +7672,16 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-2.7185</v>
+        <v>-2.8857</v>
       </c>
       <c r="C158" t="n">
-        <v>-2.0269</v>
+        <v>-2.1516</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.8617</v>
+        <v>-1.9028</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.7185</v>
+        <v>-2.8857</v>
       </c>
       <c r="F158" t="n">
         <v>-2.7185</v>
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-3.1371</v>
+        <v>-3.3995</v>
       </c>
       <c r="C159" t="n">
-        <v>-2.3391</v>
+        <v>-2.5347</v>
       </c>
       <c r="D159" t="n">
-        <v>-2.0523</v>
+        <v>-2.1323</v>
       </c>
       <c r="E159" t="n">
-        <v>-3.1371</v>
+        <v>-3.3995</v>
       </c>
       <c r="F159" t="n">
         <v>-3.1371</v>
@@ -7764,16 +7764,16 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-3.2026</v>
+        <v>-3.4851</v>
       </c>
       <c r="C160" t="n">
-        <v>-2.3879</v>
+        <v>-2.5985</v>
       </c>
       <c r="D160" t="n">
-        <v>-2.0821</v>
+        <v>-2.1705</v>
       </c>
       <c r="E160" t="n">
-        <v>-3.2026</v>
+        <v>-3.4851</v>
       </c>
       <c r="F160" t="n">
         <v>-2.4271</v>
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-5.4368</v>
+        <v>-6.0243</v>
       </c>
       <c r="C161" t="n">
-        <v>-4.0537</v>
+        <v>-4.4918</v>
       </c>
       <c r="D161" t="n">
-        <v>-3.0991</v>
+        <v>-3.3047</v>
       </c>
       <c r="E161" t="n">
-        <v>-5.4368</v>
+        <v>-6.0243</v>
       </c>
       <c r="F161" t="n">
         <v>-3.577</v>
@@ -26718,7 +26718,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>noway</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -26746,19 +26746,19 @@
         <v>24</v>
       </c>
       <c r="H472" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I472" t="n">
-        <v>0.3441</v>
+        <v>0.3796</v>
       </c>
       <c r="J472" t="n">
-        <v>8.2584</v>
+        <v>9.1104</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>noway</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -26826,13 +26826,13 @@
         <v>24</v>
       </c>
       <c r="H474" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I474" t="n">
-        <v>0.289</v>
+        <v>0.2701</v>
       </c>
       <c r="J474" t="n">
-        <v>6.936</v>
+        <v>6.4824</v>
       </c>
     </row>
     <row r="475">
@@ -26866,13 +26866,13 @@
         <v>24</v>
       </c>
       <c r="H475" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I475" t="n">
-        <v>0.1465</v>
+        <v>0.1233</v>
       </c>
       <c r="J475" t="n">
-        <v>3.516</v>
+        <v>2.9592</v>
       </c>
     </row>
     <row r="476">
@@ -26946,13 +26946,13 @@
         <v>24</v>
       </c>
       <c r="H477" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I477" t="n">
-        <v>1.5953</v>
+        <v>1.5667</v>
       </c>
       <c r="J477" t="n">
-        <v>38.2872</v>
+        <v>37.6008</v>
       </c>
     </row>
     <row r="478">
@@ -26986,13 +26986,13 @@
         <v>24</v>
       </c>
       <c r="H478" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I478" t="n">
-        <v>0.4258</v>
+        <v>0.4722</v>
       </c>
       <c r="J478" t="n">
-        <v>10.2192</v>
+        <v>11.3328</v>
       </c>
     </row>
     <row r="479">
@@ -27026,13 +27026,13 @@
         <v>24</v>
       </c>
       <c r="H479" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I479" t="n">
-        <v>0.1581</v>
+        <v>0.1885</v>
       </c>
       <c r="J479" t="n">
-        <v>3.7944</v>
+        <v>4.524</v>
       </c>
     </row>
     <row r="480">
@@ -27066,13 +27066,13 @@
         <v>24</v>
       </c>
       <c r="H480" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I480" t="n">
-        <v>-0.7383</v>
+        <v>-0.6953</v>
       </c>
       <c r="J480" t="n">
-        <v>-17.7192</v>
+        <v>-16.6872</v>
       </c>
     </row>
     <row r="481">
@@ -27109,10 +27109,10 @@
         <v>0.64</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.9502</v>
+        <v>-0.9512</v>
       </c>
       <c r="J481" t="n">
-        <v>-22.8048</v>
+        <v>-22.8288</v>
       </c>
     </row>
     <row r="482">
@@ -62558,7 +62558,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
@@ -62918,7 +62918,7 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
@@ -63358,7 +63358,7 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
@@ -72718,7 +72718,7 @@
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
@@ -73118,7 +73118,7 @@
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
@@ -73518,7 +73518,7 @@
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1642" t="inlineStr">
@@ -81518,7 +81518,7 @@
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1842" t="inlineStr">
@@ -82078,7 +82078,7 @@
     <row r="1856">
       <c r="A1856" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B1856" t="inlineStr">
